--- a/data/cleaned_data.xlsx
+++ b/data/cleaned_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5220" uniqueCount="1749">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5429" uniqueCount="1749">
   <si>
     <t>employee_id</t>
   </si>
@@ -5716,6 +5716,9 @@
       <c r="J2" t="s">
         <v>1728</v>
       </c>
+      <c r="K2" t="s">
+        <v>1731</v>
+      </c>
       <c r="L2">
         <v>0</v>
       </c>
@@ -5787,6 +5790,9 @@
       <c r="E3">
         <v>6000</v>
       </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
       <c r="G3" s="1">
         <v>51386</v>
       </c>
@@ -5870,6 +5876,9 @@
       <c r="E4">
         <v>7500.5</v>
       </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
       <c r="G4" s="1">
         <v>43909</v>
       </c>
@@ -5950,6 +5959,12 @@
       <c r="C5" t="s">
         <v>841</v>
       </c>
+      <c r="D5">
+        <v>33</v>
+      </c>
+      <c r="E5">
+        <v>6500</v>
+      </c>
       <c r="F5">
         <v>500</v>
       </c>
@@ -6024,6 +6039,9 @@
       <c r="E6">
         <v>8000</v>
       </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
       <c r="G6" s="1">
         <v>45430</v>
       </c>
@@ -6104,6 +6122,9 @@
       <c r="C7" t="s">
         <v>842</v>
       </c>
+      <c r="D7">
+        <v>33</v>
+      </c>
       <c r="E7">
         <v>6500</v>
       </c>
@@ -6264,6 +6285,15 @@
       <c r="C9" t="s">
         <v>842</v>
       </c>
+      <c r="D9">
+        <v>33</v>
+      </c>
+      <c r="E9">
+        <v>6500</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
       <c r="G9" s="1">
         <v>51039</v>
       </c>
@@ -6272,6 +6302,9 @@
       </c>
       <c r="I9" t="s">
         <v>1291</v>
+      </c>
+      <c r="J9" t="s">
+        <v>1729</v>
       </c>
       <c r="K9" t="s">
         <v>1731</v>
@@ -6323,12 +6356,18 @@
       <c r="B10" t="s">
         <v>534</v>
       </c>
+      <c r="C10" t="s">
+        <v>841</v>
+      </c>
       <c r="D10">
         <v>150</v>
       </c>
       <c r="E10">
         <v>9000</v>
       </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
       <c r="G10" s="1">
         <v>44087</v>
       </c>
@@ -6337,6 +6376,12 @@
       </c>
       <c r="I10" t="s">
         <v>1292</v>
+      </c>
+      <c r="J10" t="s">
+        <v>1729</v>
+      </c>
+      <c r="K10" t="s">
+        <v>1731</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -6572,6 +6617,12 @@
       <c r="C13" t="s">
         <v>843</v>
       </c>
+      <c r="D13">
+        <v>33</v>
+      </c>
+      <c r="E13">
+        <v>6500</v>
+      </c>
       <c r="F13">
         <v>1000</v>
       </c>
@@ -6907,6 +6958,9 @@
       <c r="E17">
         <v>6500</v>
       </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
       <c r="G17" s="1">
         <v>44744</v>
       </c>
@@ -6915,6 +6969,9 @@
       </c>
       <c r="I17" t="s">
         <v>1298</v>
+      </c>
+      <c r="J17" t="s">
+        <v>1729</v>
       </c>
       <c r="K17" t="s">
         <v>1731</v>
@@ -6990,6 +7047,9 @@
       <c r="E18">
         <v>4500</v>
       </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
       <c r="G18" s="1">
         <v>44718</v>
       </c>
@@ -7070,6 +7130,9 @@
       <c r="C19" t="s">
         <v>844</v>
       </c>
+      <c r="D19">
+        <v>33</v>
+      </c>
       <c r="E19">
         <v>5200</v>
       </c>
@@ -7242,6 +7305,9 @@
       <c r="D21">
         <v>28</v>
       </c>
+      <c r="E21">
+        <v>6500</v>
+      </c>
       <c r="F21">
         <v>300</v>
       </c>
@@ -7322,6 +7388,9 @@
       <c r="E22">
         <v>7250</v>
       </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
       <c r="G22" s="1">
         <v>43887</v>
       </c>
@@ -7330,6 +7399,9 @@
       </c>
       <c r="I22" t="s">
         <v>1303</v>
+      </c>
+      <c r="J22" t="s">
+        <v>1729</v>
       </c>
       <c r="K22" t="s">
         <v>1731</v>
@@ -7405,11 +7477,17 @@
       <c r="E23">
         <v>4800</v>
       </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
       <c r="H23" t="s">
         <v>867</v>
       </c>
       <c r="I23" t="s">
         <v>1304</v>
+      </c>
+      <c r="J23" t="s">
+        <v>1729</v>
       </c>
       <c r="K23" t="s">
         <v>1732</v>
@@ -7479,8 +7557,14 @@
       <c r="C24" t="s">
         <v>840</v>
       </c>
+      <c r="D24">
+        <v>33</v>
+      </c>
       <c r="E24">
         <v>9500</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
       </c>
       <c r="G24" s="1">
         <v>44070</v>
@@ -7556,11 +7640,20 @@
       <c r="D25">
         <v>125</v>
       </c>
+      <c r="E25">
+        <v>6500</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
       <c r="H25" t="s">
         <v>869</v>
       </c>
       <c r="I25" t="s">
         <v>1306</v>
+      </c>
+      <c r="J25" t="s">
+        <v>1729</v>
       </c>
       <c r="K25" t="s">
         <v>1731</v>
@@ -7624,6 +7717,9 @@
       <c r="E26">
         <v>5750</v>
       </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
       <c r="G26" s="1">
         <v>44831</v>
       </c>
@@ -7635,6 +7731,9 @@
       </c>
       <c r="J26" t="s">
         <v>1729</v>
+      </c>
+      <c r="K26" t="s">
+        <v>1731</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -7704,6 +7803,9 @@
       <c r="E27">
         <v>6000</v>
       </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
       <c r="G27" s="1">
         <v>44157</v>
       </c>
@@ -7790,6 +7892,9 @@
       <c r="E28">
         <v>8200</v>
       </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
       <c r="G28" s="1">
         <v>43843</v>
       </c>
@@ -7861,6 +7966,9 @@
       <c r="C29" t="s">
         <v>842</v>
       </c>
+      <c r="D29">
+        <v>33</v>
+      </c>
       <c r="E29">
         <v>-1000</v>
       </c>
@@ -7878,6 +7986,9 @@
       </c>
       <c r="J29" t="s">
         <v>1728</v>
+      </c>
+      <c r="K29" t="s">
+        <v>1731</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -8024,6 +8135,9 @@
       <c r="D31">
         <v>38</v>
       </c>
+      <c r="E31">
+        <v>6500</v>
+      </c>
       <c r="F31">
         <v>250</v>
       </c>
@@ -8035,6 +8149,9 @@
       </c>
       <c r="I31" t="s">
         <v>1311</v>
+      </c>
+      <c r="J31" t="s">
+        <v>1729</v>
       </c>
       <c r="K31" t="s">
         <v>1731</v>
@@ -8095,6 +8212,9 @@
       <c r="C32" t="s">
         <v>843</v>
       </c>
+      <c r="D32">
+        <v>33</v>
+      </c>
       <c r="E32">
         <v>6500</v>
       </c>
@@ -8433,6 +8553,12 @@
       <c r="C36" t="s">
         <v>840</v>
       </c>
+      <c r="D36">
+        <v>33</v>
+      </c>
+      <c r="E36">
+        <v>6500</v>
+      </c>
       <c r="F36">
         <v>250</v>
       </c>
@@ -8679,6 +8805,9 @@
       <c r="E39">
         <v>4500</v>
       </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
       <c r="I39" t="s">
         <v>1319</v>
       </c>
@@ -8753,6 +8882,12 @@
       <c r="D40">
         <v>200</v>
       </c>
+      <c r="E40">
+        <v>6500</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
       <c r="G40" s="1">
         <v>44325</v>
       </c>
@@ -8761,6 +8896,9 @@
       </c>
       <c r="I40" t="s">
         <v>1320</v>
+      </c>
+      <c r="J40" t="s">
+        <v>1729</v>
       </c>
       <c r="K40" t="s">
         <v>1731</v>
@@ -8824,6 +8962,9 @@
       <c r="E41">
         <v>5000</v>
       </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
       <c r="G41" s="1">
         <v>44055</v>
       </c>
@@ -8922,6 +9063,12 @@
       <c r="I42" t="s">
         <v>1322</v>
       </c>
+      <c r="J42" t="s">
+        <v>1729</v>
+      </c>
+      <c r="K42" t="s">
+        <v>1731</v>
+      </c>
       <c r="L42">
         <v>0</v>
       </c>
@@ -8987,6 +9134,9 @@
       <c r="C43" t="s">
         <v>844</v>
       </c>
+      <c r="D43">
+        <v>33</v>
+      </c>
       <c r="E43">
         <v>7100</v>
       </c>
@@ -9153,9 +9303,15 @@
       <c r="C45" t="s">
         <v>842</v>
       </c>
+      <c r="D45">
+        <v>33</v>
+      </c>
       <c r="E45">
         <v>-250</v>
       </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
       <c r="G45" s="1">
         <v>43621</v>
       </c>
@@ -9164,6 +9320,9 @@
       </c>
       <c r="I45" t="s">
         <v>1324</v>
+      </c>
+      <c r="J45" t="s">
+        <v>1729</v>
       </c>
       <c r="K45" t="s">
         <v>1732</v>
@@ -9233,6 +9392,9 @@
       <c r="E46">
         <v>6200</v>
       </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
       <c r="G46" s="1">
         <v>44394</v>
       </c>
@@ -9316,6 +9478,9 @@
       <c r="D47">
         <v>46</v>
       </c>
+      <c r="E47">
+        <v>6500</v>
+      </c>
       <c r="F47">
         <v>500</v>
       </c>
@@ -9396,6 +9561,9 @@
       <c r="E48">
         <v>8500</v>
       </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
       <c r="G48" s="1">
         <v>43577</v>
       </c>
@@ -9404,6 +9572,12 @@
       </c>
       <c r="I48" t="s">
         <v>1327</v>
+      </c>
+      <c r="J48" t="s">
+        <v>1729</v>
+      </c>
+      <c r="K48" t="s">
+        <v>1731</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -9476,6 +9650,9 @@
       <c r="E49">
         <v>7000</v>
       </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
       <c r="G49" s="1">
         <v>44248</v>
       </c>
@@ -9574,6 +9751,9 @@
       <c r="I50" t="s">
         <v>1329</v>
       </c>
+      <c r="J50" t="s">
+        <v>1729</v>
+      </c>
       <c r="K50" t="s">
         <v>1731</v>
       </c>
@@ -9642,6 +9822,9 @@
       <c r="D51">
         <v>-10</v>
       </c>
+      <c r="E51">
+        <v>6500</v>
+      </c>
       <c r="F51">
         <v>1000</v>
       </c>
@@ -9653,6 +9836,9 @@
       </c>
       <c r="I51" t="s">
         <v>1330</v>
+      </c>
+      <c r="J51" t="s">
+        <v>1729</v>
       </c>
       <c r="K51" t="s">
         <v>1732</v>
@@ -9716,6 +9902,9 @@
       <c r="E52">
         <v>6000</v>
       </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
       <c r="G52" s="1">
         <v>43739</v>
       </c>
@@ -9885,6 +10074,9 @@
       <c r="C54" t="s">
         <v>841</v>
       </c>
+      <c r="D54">
+        <v>33</v>
+      </c>
       <c r="E54">
         <v>5200</v>
       </c>
@@ -9899,6 +10091,9 @@
       </c>
       <c r="J54" t="s">
         <v>1730</v>
+      </c>
+      <c r="K54" t="s">
+        <v>1731</v>
       </c>
       <c r="L54">
         <v>1</v>
@@ -9956,6 +10151,12 @@
       <c r="C55" t="s">
         <v>845</v>
       </c>
+      <c r="D55">
+        <v>33</v>
+      </c>
+      <c r="E55">
+        <v>6500</v>
+      </c>
       <c r="F55">
         <v>1250</v>
       </c>
@@ -10039,6 +10240,9 @@
       <c r="H56" t="s">
         <v>896</v>
       </c>
+      <c r="J56" t="s">
+        <v>1729</v>
+      </c>
       <c r="K56" t="s">
         <v>1731</v>
       </c>
@@ -10196,6 +10400,9 @@
       <c r="E58">
         <v>6500</v>
       </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
       <c r="G58" s="1">
         <v>45432</v>
       </c>
@@ -10204,6 +10411,9 @@
       </c>
       <c r="I58" t="s">
         <v>1336</v>
+      </c>
+      <c r="J58" t="s">
+        <v>1729</v>
       </c>
       <c r="K58" t="s">
         <v>1732</v>
@@ -10279,6 +10489,9 @@
       <c r="E59">
         <v>7200</v>
       </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
       <c r="G59" s="1">
         <v>45283</v>
       </c>
@@ -10287,6 +10500,9 @@
       </c>
       <c r="I59" t="s">
         <v>1337</v>
+      </c>
+      <c r="J59" t="s">
+        <v>1729</v>
       </c>
       <c r="K59" t="s">
         <v>1732</v>
@@ -10356,6 +10572,9 @@
       <c r="D60">
         <v>35</v>
       </c>
+      <c r="E60">
+        <v>6500</v>
+      </c>
       <c r="F60">
         <v>-200</v>
       </c>
@@ -10370,6 +10589,9 @@
       </c>
       <c r="J60" t="s">
         <v>1728</v>
+      </c>
+      <c r="K60" t="s">
+        <v>1731</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -10433,6 +10655,9 @@
       <c r="E61">
         <v>5750</v>
       </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
       <c r="H61" t="s">
         <v>901</v>
       </c>
@@ -10441,6 +10666,9 @@
       </c>
       <c r="J61" t="s">
         <v>1728</v>
+      </c>
+      <c r="K61" t="s">
+        <v>1731</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -10507,6 +10735,9 @@
       <c r="C62" t="s">
         <v>845</v>
       </c>
+      <c r="D62">
+        <v>33</v>
+      </c>
       <c r="E62">
         <v>-3000</v>
       </c>
@@ -10518,6 +10749,9 @@
       </c>
       <c r="H62" t="s">
         <v>902</v>
+      </c>
+      <c r="J62" t="s">
+        <v>1729</v>
       </c>
       <c r="K62" t="s">
         <v>1732</v>
@@ -10676,6 +10910,9 @@
       <c r="E64">
         <v>6500</v>
       </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
       <c r="H64" t="s">
         <v>904</v>
       </c>
@@ -10753,6 +10990,15 @@
       <c r="C65" t="s">
         <v>842</v>
       </c>
+      <c r="D65">
+        <v>33</v>
+      </c>
+      <c r="E65">
+        <v>6500</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
       <c r="G65" s="1">
         <v>45291</v>
       </c>
@@ -10764,6 +11010,9 @@
       </c>
       <c r="J65" t="s">
         <v>1730</v>
+      </c>
+      <c r="K65" t="s">
+        <v>1731</v>
       </c>
       <c r="L65">
         <v>1</v>
@@ -10821,6 +11070,9 @@
       <c r="E66">
         <v>9200</v>
       </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
       <c r="G66" s="1">
         <v>44395</v>
       </c>
@@ -10999,6 +11251,9 @@
       <c r="H68" t="s">
         <v>907</v>
       </c>
+      <c r="J68" t="s">
+        <v>1729</v>
+      </c>
       <c r="K68" t="s">
         <v>1731</v>
       </c>
@@ -11067,6 +11322,9 @@
       <c r="D69">
         <v>250</v>
       </c>
+      <c r="E69">
+        <v>6500</v>
+      </c>
       <c r="F69">
         <v>300</v>
       </c>
@@ -11156,6 +11414,9 @@
       <c r="J70" t="s">
         <v>1728</v>
       </c>
+      <c r="K70" t="s">
+        <v>1731</v>
+      </c>
       <c r="L70">
         <v>0</v>
       </c>
@@ -11218,6 +11479,9 @@
       <c r="C71" t="s">
         <v>841</v>
       </c>
+      <c r="D71">
+        <v>33</v>
+      </c>
       <c r="E71">
         <v>4800</v>
       </c>
@@ -11316,6 +11580,9 @@
       <c r="J72" t="s">
         <v>1728</v>
       </c>
+      <c r="K72" t="s">
+        <v>1731</v>
+      </c>
       <c r="L72">
         <v>0</v>
       </c>
@@ -11384,6 +11651,12 @@
       <c r="D73">
         <v>20</v>
       </c>
+      <c r="E73">
+        <v>6500</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
       <c r="G73" s="1">
         <v>44239</v>
       </c>
@@ -11455,8 +11728,14 @@
       <c r="C74" t="s">
         <v>841</v>
       </c>
+      <c r="D74">
+        <v>33</v>
+      </c>
       <c r="E74">
         <v>5250</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
       </c>
       <c r="G74" s="1">
         <v>43695</v>
@@ -11624,6 +11903,9 @@
       <c r="E76">
         <v>7200</v>
       </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
       <c r="G76" s="1">
         <v>44471</v>
       </c>
@@ -11719,6 +12001,9 @@
       <c r="H77" t="s">
         <v>915</v>
       </c>
+      <c r="J77" t="s">
+        <v>1729</v>
+      </c>
       <c r="K77" t="s">
         <v>1732</v>
       </c>
@@ -11790,11 +12075,20 @@
       <c r="D78">
         <v>-1</v>
       </c>
+      <c r="E78">
+        <v>6500</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
       <c r="H78" t="s">
         <v>916</v>
       </c>
       <c r="I78" t="s">
         <v>1352</v>
+      </c>
+      <c r="J78" t="s">
+        <v>1729</v>
       </c>
       <c r="K78" t="s">
         <v>1731</v>
@@ -11858,6 +12152,9 @@
       <c r="E79">
         <v>6500</v>
       </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
       <c r="G79" s="1">
         <v>45445</v>
       </c>
@@ -11869,6 +12166,9 @@
       </c>
       <c r="J79" t="s">
         <v>1729</v>
+      </c>
+      <c r="K79" t="s">
+        <v>1731</v>
       </c>
       <c r="L79">
         <v>0</v>
@@ -11935,6 +12235,9 @@
       <c r="C80" t="s">
         <v>841</v>
       </c>
+      <c r="D80">
+        <v>33</v>
+      </c>
       <c r="E80">
         <v>4500</v>
       </c>
@@ -11952,6 +12255,9 @@
       </c>
       <c r="J80" t="s">
         <v>1729</v>
+      </c>
+      <c r="K80" t="s">
+        <v>1731</v>
       </c>
       <c r="L80">
         <v>1</v>
@@ -12012,6 +12318,9 @@
       <c r="D81">
         <v>23</v>
       </c>
+      <c r="E81">
+        <v>6500</v>
+      </c>
       <c r="F81">
         <v>750</v>
       </c>
@@ -12178,11 +12487,17 @@
       <c r="E83">
         <v>5500</v>
       </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
       <c r="G83" s="1">
         <v>44584</v>
       </c>
       <c r="H83" t="s">
         <v>921</v>
+      </c>
+      <c r="J83" t="s">
+        <v>1729</v>
       </c>
       <c r="K83" t="s">
         <v>1732</v>
@@ -12341,6 +12656,9 @@
       <c r="C85" t="s">
         <v>843</v>
       </c>
+      <c r="D85">
+        <v>33</v>
+      </c>
       <c r="E85">
         <v>9000</v>
       </c>
@@ -12424,6 +12742,9 @@
       <c r="D86">
         <v>52</v>
       </c>
+      <c r="E86">
+        <v>6500</v>
+      </c>
       <c r="F86">
         <v>750</v>
       </c>
@@ -12435,6 +12756,9 @@
       </c>
       <c r="I86" t="s">
         <v>1358</v>
+      </c>
+      <c r="J86" t="s">
+        <v>1729</v>
       </c>
       <c r="K86" t="s">
         <v>1731</v>
@@ -12587,6 +12911,9 @@
       <c r="E88">
         <v>7500</v>
       </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
       <c r="G88" s="1">
         <v>44443</v>
       </c>
@@ -12667,6 +12994,9 @@
       <c r="D89">
         <v>27</v>
       </c>
+      <c r="E89">
+        <v>6500</v>
+      </c>
       <c r="F89">
         <v>300</v>
       </c>
@@ -12830,6 +13160,9 @@
       <c r="E91">
         <v>5200</v>
       </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
       <c r="H91" t="s">
         <v>929</v>
       </c>
@@ -12907,9 +13240,15 @@
       <c r="C92" t="s">
         <v>842</v>
       </c>
+      <c r="D92">
+        <v>33</v>
+      </c>
       <c r="E92">
         <v>6500</v>
       </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
       <c r="G92" s="1">
         <v>45225</v>
       </c>
@@ -12921,6 +13260,9 @@
       </c>
       <c r="J92" t="s">
         <v>1728</v>
+      </c>
+      <c r="K92" t="s">
+        <v>1731</v>
       </c>
       <c r="L92">
         <v>1</v>
@@ -13073,6 +13415,9 @@
       <c r="D94">
         <v>38</v>
       </c>
+      <c r="E94">
+        <v>6500</v>
+      </c>
       <c r="F94">
         <v>1250</v>
       </c>
@@ -13084,6 +13429,9 @@
       </c>
       <c r="I94" t="s">
         <v>1364</v>
+      </c>
+      <c r="J94" t="s">
+        <v>1729</v>
       </c>
       <c r="K94" t="s">
         <v>1731</v>
@@ -13144,6 +13492,9 @@
       <c r="C95" t="s">
         <v>840</v>
       </c>
+      <c r="D95">
+        <v>33</v>
+      </c>
       <c r="E95">
         <v>5800</v>
       </c>
@@ -13242,6 +13593,9 @@
       <c r="J96" t="s">
         <v>1729</v>
       </c>
+      <c r="K96" t="s">
+        <v>1731</v>
+      </c>
       <c r="L96">
         <v>0</v>
       </c>
@@ -13310,6 +13664,9 @@
       <c r="D97">
         <v>29</v>
       </c>
+      <c r="E97">
+        <v>6500</v>
+      </c>
       <c r="F97">
         <v>1000</v>
       </c>
@@ -13321,6 +13678,9 @@
       </c>
       <c r="I97" t="s">
         <v>1367</v>
+      </c>
+      <c r="J97" t="s">
+        <v>1729</v>
       </c>
       <c r="K97" t="s">
         <v>1732</v>
@@ -13402,6 +13762,9 @@
       <c r="J98" t="s">
         <v>1729</v>
       </c>
+      <c r="K98" t="s">
+        <v>1731</v>
+      </c>
       <c r="L98">
         <v>0</v>
       </c>
@@ -13657,6 +14020,9 @@
       <c r="I101" t="s">
         <v>1371</v>
       </c>
+      <c r="J101" t="s">
+        <v>1729</v>
+      </c>
       <c r="K101" t="s">
         <v>1732</v>
       </c>
@@ -13725,6 +14091,9 @@
       <c r="D102">
         <v>40</v>
       </c>
+      <c r="E102">
+        <v>6500</v>
+      </c>
       <c r="F102">
         <v>500</v>
       </c>
@@ -13736,6 +14105,9 @@
       </c>
       <c r="I102" t="s">
         <v>1372</v>
+      </c>
+      <c r="J102" t="s">
+        <v>1729</v>
       </c>
       <c r="K102" t="s">
         <v>1731</v>
@@ -13796,6 +14168,9 @@
       <c r="C103" t="s">
         <v>844</v>
       </c>
+      <c r="D103">
+        <v>33</v>
+      </c>
       <c r="E103">
         <v>7200</v>
       </c>
@@ -13807,6 +14182,9 @@
       </c>
       <c r="H103" t="s">
         <v>940</v>
+      </c>
+      <c r="J103" t="s">
+        <v>1729</v>
       </c>
       <c r="K103" t="s">
         <v>1732</v>
@@ -13870,6 +14248,9 @@
       <c r="C104" t="s">
         <v>843</v>
       </c>
+      <c r="D104">
+        <v>33</v>
+      </c>
       <c r="E104">
         <v>4750</v>
       </c>
@@ -13956,6 +14337,9 @@
       <c r="E105">
         <v>6000</v>
       </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
       <c r="G105" s="1">
         <v>45043</v>
       </c>
@@ -14039,6 +14423,12 @@
       <c r="D106">
         <v>43</v>
       </c>
+      <c r="E106">
+        <v>6500</v>
+      </c>
+      <c r="F106">
+        <v>0</v>
+      </c>
       <c r="G106" s="1">
         <v>43752</v>
       </c>
@@ -14047,6 +14437,9 @@
       </c>
       <c r="I106" t="s">
         <v>1375</v>
+      </c>
+      <c r="J106" t="s">
+        <v>1729</v>
       </c>
       <c r="K106" t="s">
         <v>1732</v>
@@ -14282,8 +14675,14 @@
       <c r="C109" t="s">
         <v>843</v>
       </c>
+      <c r="D109">
+        <v>33</v>
+      </c>
       <c r="E109">
         <v>7000</v>
+      </c>
+      <c r="F109">
+        <v>0</v>
       </c>
       <c r="G109" s="1">
         <v>45420</v>
@@ -14362,6 +14761,9 @@
       <c r="D110">
         <v>56</v>
       </c>
+      <c r="E110">
+        <v>6500</v>
+      </c>
       <c r="F110">
         <v>1000</v>
       </c>
@@ -14442,6 +14844,9 @@
       <c r="E111">
         <v>6250</v>
       </c>
+      <c r="F111">
+        <v>0</v>
+      </c>
       <c r="G111" s="1">
         <v>43712</v>
       </c>
@@ -14697,6 +15102,12 @@
       <c r="D114">
         <v>39</v>
       </c>
+      <c r="E114">
+        <v>6500</v>
+      </c>
+      <c r="F114">
+        <v>0</v>
+      </c>
       <c r="H114" t="s">
         <v>951</v>
       </c>
@@ -14765,6 +15176,9 @@
       <c r="C115" t="s">
         <v>841</v>
       </c>
+      <c r="D115">
+        <v>33</v>
+      </c>
       <c r="E115">
         <v>7500</v>
       </c>
@@ -14779,6 +15193,9 @@
       </c>
       <c r="I115" t="s">
         <v>1384</v>
+      </c>
+      <c r="J115" t="s">
+        <v>1729</v>
       </c>
       <c r="K115" t="s">
         <v>1732</v>
@@ -14848,6 +15265,9 @@
       <c r="E116">
         <v>6500</v>
       </c>
+      <c r="F116">
+        <v>0</v>
+      </c>
       <c r="G116" s="1">
         <v>43971</v>
       </c>
@@ -15103,6 +15523,12 @@
       <c r="C119" t="s">
         <v>841</v>
       </c>
+      <c r="D119">
+        <v>33</v>
+      </c>
+      <c r="E119">
+        <v>6500</v>
+      </c>
       <c r="F119">
         <v>1250</v>
       </c>
@@ -15266,6 +15692,9 @@
       <c r="E121">
         <v>6800</v>
       </c>
+      <c r="F121">
+        <v>0</v>
+      </c>
       <c r="G121" s="1">
         <v>45547</v>
       </c>
@@ -15274,6 +15703,9 @@
       </c>
       <c r="I121" t="s">
         <v>1390</v>
+      </c>
+      <c r="J121" t="s">
+        <v>1729</v>
       </c>
       <c r="K121" t="s">
         <v>1732</v>
@@ -15349,6 +15781,9 @@
       <c r="E122">
         <v>5200</v>
       </c>
+      <c r="F122">
+        <v>0</v>
+      </c>
       <c r="G122" s="1">
         <v>44642</v>
       </c>
@@ -15429,6 +15864,15 @@
       <c r="C123" t="s">
         <v>844</v>
       </c>
+      <c r="D123">
+        <v>33</v>
+      </c>
+      <c r="E123">
+        <v>6500</v>
+      </c>
+      <c r="F123">
+        <v>0</v>
+      </c>
       <c r="G123" s="1">
         <v>45429</v>
       </c>
@@ -15500,6 +15944,9 @@
       <c r="E124">
         <v>9250</v>
       </c>
+      <c r="F124">
+        <v>0</v>
+      </c>
       <c r="G124" s="1">
         <v>44643</v>
       </c>
@@ -15669,6 +16116,9 @@
       <c r="C126" t="s">
         <v>843</v>
       </c>
+      <c r="D126">
+        <v>33</v>
+      </c>
       <c r="E126">
         <v>4500</v>
       </c>
@@ -15683,6 +16133,9 @@
       </c>
       <c r="I126" t="s">
         <v>1395</v>
+      </c>
+      <c r="J126" t="s">
+        <v>1729</v>
       </c>
       <c r="K126" t="s">
         <v>1731</v>
@@ -15749,6 +16202,9 @@
       <c r="D127">
         <v>33</v>
       </c>
+      <c r="E127">
+        <v>6500</v>
+      </c>
       <c r="F127">
         <v>750</v>
       </c>
@@ -15841,6 +16297,9 @@
       <c r="I128" t="s">
         <v>1397</v>
       </c>
+      <c r="J128" t="s">
+        <v>1729</v>
+      </c>
       <c r="K128" t="s">
         <v>1731</v>
       </c>
@@ -15912,6 +16371,9 @@
       <c r="E129">
         <v>7500</v>
       </c>
+      <c r="F129">
+        <v>0</v>
+      </c>
       <c r="G129" s="1">
         <v>45165</v>
       </c>
@@ -15920,6 +16382,9 @@
       </c>
       <c r="I129" t="s">
         <v>1398</v>
+      </c>
+      <c r="J129" t="s">
+        <v>1729</v>
       </c>
       <c r="K129" t="s">
         <v>1732</v>
@@ -15989,6 +16454,9 @@
       <c r="E130">
         <v>6250</v>
       </c>
+      <c r="F130">
+        <v>0</v>
+      </c>
       <c r="G130" s="1">
         <v>45062</v>
       </c>
@@ -16072,6 +16540,12 @@
       <c r="D131">
         <v>31</v>
       </c>
+      <c r="E131">
+        <v>6500</v>
+      </c>
+      <c r="F131">
+        <v>0</v>
+      </c>
       <c r="G131" s="1">
         <v>44708</v>
       </c>
@@ -16161,6 +16635,12 @@
       <c r="I132" t="s">
         <v>1401</v>
       </c>
+      <c r="J132" t="s">
+        <v>1729</v>
+      </c>
+      <c r="K132" t="s">
+        <v>1731</v>
+      </c>
       <c r="L132">
         <v>0</v>
       </c>
@@ -16315,8 +16795,14 @@
       <c r="C134" t="s">
         <v>841</v>
       </c>
+      <c r="D134">
+        <v>33</v>
+      </c>
       <c r="E134">
         <v>7200</v>
+      </c>
+      <c r="F134">
+        <v>0</v>
       </c>
       <c r="G134" s="1">
         <v>44988</v>
@@ -16395,6 +16881,12 @@
       <c r="D135">
         <v>170</v>
       </c>
+      <c r="E135">
+        <v>6500</v>
+      </c>
+      <c r="F135">
+        <v>0</v>
+      </c>
       <c r="G135" s="1">
         <v>44524</v>
       </c>
@@ -16552,6 +17044,9 @@
       <c r="C137" t="s">
         <v>843</v>
       </c>
+      <c r="D137">
+        <v>33</v>
+      </c>
       <c r="E137">
         <v>9000</v>
       </c>
@@ -16724,6 +17219,9 @@
       <c r="D139">
         <v>44</v>
       </c>
+      <c r="E139">
+        <v>6500</v>
+      </c>
       <c r="F139">
         <v>-200</v>
       </c>
@@ -16804,11 +17302,17 @@
       <c r="E140">
         <v>4800</v>
       </c>
+      <c r="F140">
+        <v>0</v>
+      </c>
       <c r="G140" s="1">
         <v>44912</v>
       </c>
       <c r="H140" t="s">
         <v>975</v>
+      </c>
+      <c r="J140" t="s">
+        <v>1729</v>
       </c>
       <c r="K140" t="s">
         <v>1731</v>
@@ -16878,6 +17382,9 @@
       <c r="C141" t="s">
         <v>844</v>
       </c>
+      <c r="D141">
+        <v>33</v>
+      </c>
       <c r="E141">
         <v>7200</v>
       </c>
@@ -16892,6 +17399,9 @@
       </c>
       <c r="I141" t="s">
         <v>1409</v>
+      </c>
+      <c r="J141" t="s">
+        <v>1729</v>
       </c>
       <c r="K141" t="s">
         <v>1732</v>
@@ -16958,6 +17468,9 @@
       <c r="E142">
         <v>6500</v>
       </c>
+      <c r="F142">
+        <v>0</v>
+      </c>
       <c r="G142" s="1">
         <v>44042</v>
       </c>
@@ -17041,6 +17554,12 @@
       <c r="D143">
         <v>32</v>
       </c>
+      <c r="E143">
+        <v>6500</v>
+      </c>
+      <c r="F143">
+        <v>0</v>
+      </c>
       <c r="G143" s="1">
         <v>45191</v>
       </c>
@@ -17112,8 +17631,14 @@
       <c r="C144" t="s">
         <v>843</v>
       </c>
+      <c r="D144">
+        <v>33</v>
+      </c>
       <c r="E144">
         <v>8500</v>
+      </c>
+      <c r="F144">
+        <v>0</v>
       </c>
       <c r="G144" s="1">
         <v>45267</v>
@@ -17195,6 +17720,9 @@
       <c r="E145">
         <v>5250</v>
       </c>
+      <c r="F145">
+        <v>0</v>
+      </c>
       <c r="G145" s="1">
         <v>44761</v>
       </c>
@@ -17203,6 +17731,9 @@
       </c>
       <c r="I145" t="s">
         <v>1413</v>
+      </c>
+      <c r="J145" t="s">
+        <v>1729</v>
       </c>
       <c r="K145" t="s">
         <v>1732</v>
@@ -17364,6 +17895,12 @@
       <c r="D147">
         <v>30</v>
       </c>
+      <c r="E147">
+        <v>6500</v>
+      </c>
+      <c r="F147">
+        <v>0</v>
+      </c>
       <c r="G147" s="1">
         <v>44553</v>
       </c>
@@ -17438,6 +17975,9 @@
       <c r="E148">
         <v>7750</v>
       </c>
+      <c r="F148">
+        <v>0</v>
+      </c>
       <c r="G148" s="1">
         <v>44746</v>
       </c>
@@ -17533,6 +18073,9 @@
       <c r="I149" t="s">
         <v>1416</v>
       </c>
+      <c r="J149" t="s">
+        <v>1729</v>
+      </c>
       <c r="K149" t="s">
         <v>1731</v>
       </c>
@@ -17622,6 +18165,9 @@
       <c r="J150" t="s">
         <v>1728</v>
       </c>
+      <c r="K150" t="s">
+        <v>1731</v>
+      </c>
       <c r="L150">
         <v>0</v>
       </c>
@@ -17687,6 +18233,9 @@
       <c r="C151" t="s">
         <v>842</v>
       </c>
+      <c r="D151">
+        <v>33</v>
+      </c>
       <c r="E151">
         <v>6000</v>
       </c>
@@ -17770,6 +18319,12 @@
       <c r="D152">
         <v>37</v>
       </c>
+      <c r="E152">
+        <v>6500</v>
+      </c>
+      <c r="F152">
+        <v>0</v>
+      </c>
       <c r="G152" s="1">
         <v>44800</v>
       </c>
@@ -17847,6 +18402,9 @@
       <c r="E153">
         <v>9000</v>
       </c>
+      <c r="F153">
+        <v>0</v>
+      </c>
       <c r="G153" s="1">
         <v>45654</v>
       </c>
@@ -17924,6 +18482,9 @@
       <c r="C154" t="s">
         <v>840</v>
       </c>
+      <c r="D154">
+        <v>33</v>
+      </c>
       <c r="E154">
         <v>5500</v>
       </c>
@@ -18087,6 +18648,9 @@
       <c r="D156">
         <v>23</v>
       </c>
+      <c r="E156">
+        <v>6500</v>
+      </c>
       <c r="F156">
         <v>500</v>
       </c>
@@ -18167,6 +18731,9 @@
       <c r="E157">
         <v>8200</v>
       </c>
+      <c r="F157">
+        <v>0</v>
+      </c>
       <c r="G157" s="1">
         <v>43605</v>
       </c>
@@ -18175,6 +18742,12 @@
       </c>
       <c r="I157" t="s">
         <v>1421</v>
+      </c>
+      <c r="J157" t="s">
+        <v>1729</v>
+      </c>
+      <c r="K157" t="s">
+        <v>1731</v>
       </c>
       <c r="L157">
         <v>0</v>
@@ -18244,6 +18817,9 @@
       <c r="E158">
         <v>5200</v>
       </c>
+      <c r="F158">
+        <v>0</v>
+      </c>
       <c r="G158" s="1">
         <v>43659</v>
       </c>
@@ -18330,6 +18906,9 @@
       <c r="E159">
         <v>7000</v>
       </c>
+      <c r="F159">
+        <v>0</v>
+      </c>
       <c r="G159" s="1">
         <v>44095</v>
       </c>
@@ -18413,6 +18992,9 @@
       <c r="D160">
         <v>26</v>
       </c>
+      <c r="E160">
+        <v>6500</v>
+      </c>
       <c r="F160">
         <v>750</v>
       </c>
@@ -18493,6 +19075,9 @@
       <c r="E161">
         <v>6750</v>
       </c>
+      <c r="F161">
+        <v>0</v>
+      </c>
       <c r="G161" s="1">
         <v>44539</v>
       </c>
@@ -18570,6 +19155,9 @@
       <c r="C162" t="s">
         <v>845</v>
       </c>
+      <c r="D162">
+        <v>33</v>
+      </c>
       <c r="E162">
         <v>4500</v>
       </c>
@@ -18584,6 +19172,9 @@
       </c>
       <c r="I162" t="s">
         <v>1425</v>
+      </c>
+      <c r="J162" t="s">
+        <v>1729</v>
       </c>
       <c r="K162" t="s">
         <v>1731</v>
@@ -18647,6 +19238,15 @@
       <c r="C163" t="s">
         <v>843</v>
       </c>
+      <c r="D163">
+        <v>33</v>
+      </c>
+      <c r="E163">
+        <v>6500</v>
+      </c>
+      <c r="F163">
+        <v>0</v>
+      </c>
       <c r="G163" s="1">
         <v>45499</v>
       </c>
@@ -18718,6 +19318,9 @@
       <c r="E164">
         <v>9500</v>
       </c>
+      <c r="F164">
+        <v>0</v>
+      </c>
       <c r="G164" s="1">
         <v>43723</v>
       </c>
@@ -18804,6 +19407,9 @@
       <c r="E165">
         <v>6000</v>
       </c>
+      <c r="F165">
+        <v>0</v>
+      </c>
       <c r="G165" s="1">
         <v>44112</v>
       </c>
@@ -18890,6 +19496,9 @@
       <c r="E166">
         <v>7200</v>
       </c>
+      <c r="F166">
+        <v>0</v>
+      </c>
       <c r="G166" s="1">
         <v>43843</v>
       </c>
@@ -18898,6 +19507,12 @@
       </c>
       <c r="I166" t="s">
         <v>1429</v>
+      </c>
+      <c r="J166" t="s">
+        <v>1729</v>
+      </c>
+      <c r="K166" t="s">
+        <v>1731</v>
       </c>
       <c r="L166">
         <v>0</v>
@@ -18964,14 +19579,23 @@
       <c r="C167" t="s">
         <v>842</v>
       </c>
+      <c r="D167">
+        <v>33</v>
+      </c>
       <c r="E167">
         <v>5000</v>
       </c>
+      <c r="F167">
+        <v>0</v>
+      </c>
       <c r="G167" s="1">
         <v>45624</v>
       </c>
       <c r="H167" t="s">
         <v>999</v>
+      </c>
+      <c r="J167" t="s">
+        <v>1729</v>
       </c>
       <c r="K167" t="s">
         <v>1732</v>
@@ -19035,6 +19659,9 @@
       <c r="D168">
         <v>29</v>
       </c>
+      <c r="E168">
+        <v>6500</v>
+      </c>
       <c r="F168">
         <v>-50</v>
       </c>
@@ -19112,6 +19739,9 @@
       <c r="E169">
         <v>8200</v>
       </c>
+      <c r="F169">
+        <v>0</v>
+      </c>
       <c r="G169" s="1">
         <v>43868</v>
       </c>
@@ -19189,6 +19819,12 @@
       <c r="C170" t="s">
         <v>845</v>
       </c>
+      <c r="D170">
+        <v>33</v>
+      </c>
+      <c r="E170">
+        <v>6500</v>
+      </c>
       <c r="F170">
         <v>300</v>
       </c>
@@ -19278,6 +19914,9 @@
       <c r="J171" t="s">
         <v>1729</v>
       </c>
+      <c r="K171" t="s">
+        <v>1731</v>
+      </c>
       <c r="L171">
         <v>0</v>
       </c>
@@ -19346,6 +19985,9 @@
       <c r="E172">
         <v>5500</v>
       </c>
+      <c r="F172">
+        <v>0</v>
+      </c>
       <c r="G172" s="1">
         <v>45473</v>
       </c>
@@ -19432,6 +20074,9 @@
       <c r="E173">
         <v>-1000</v>
       </c>
+      <c r="F173">
+        <v>0</v>
+      </c>
       <c r="G173" s="1">
         <v>44923</v>
       </c>
@@ -19443,6 +20088,9 @@
       </c>
       <c r="J173" t="s">
         <v>1728</v>
+      </c>
+      <c r="K173" t="s">
+        <v>1731</v>
       </c>
       <c r="L173">
         <v>0</v>
@@ -19524,6 +20172,9 @@
       <c r="J174" t="s">
         <v>1728</v>
       </c>
+      <c r="K174" t="s">
+        <v>1731</v>
+      </c>
       <c r="L174">
         <v>0</v>
       </c>
@@ -19592,6 +20243,12 @@
       <c r="D175">
         <v>40</v>
       </c>
+      <c r="E175">
+        <v>6500</v>
+      </c>
+      <c r="F175">
+        <v>0</v>
+      </c>
       <c r="G175" s="1">
         <v>44912</v>
       </c>
@@ -19603,6 +20260,9 @@
       </c>
       <c r="J175" t="s">
         <v>1728</v>
+      </c>
+      <c r="K175" t="s">
+        <v>1731</v>
       </c>
       <c r="L175">
         <v>0</v>
@@ -19660,8 +20320,14 @@
       <c r="C176" t="s">
         <v>841</v>
       </c>
+      <c r="D176">
+        <v>33</v>
+      </c>
       <c r="E176">
         <v>9000</v>
+      </c>
+      <c r="F176">
+        <v>0</v>
       </c>
       <c r="G176" s="1">
         <v>45053</v>
@@ -19832,6 +20498,9 @@
       <c r="E178">
         <v>6800</v>
       </c>
+      <c r="F178">
+        <v>0</v>
+      </c>
       <c r="G178" s="1">
         <v>44744</v>
       </c>
@@ -19912,6 +20581,15 @@
       <c r="C179" t="s">
         <v>841</v>
       </c>
+      <c r="D179">
+        <v>33</v>
+      </c>
+      <c r="E179">
+        <v>6500</v>
+      </c>
+      <c r="F179">
+        <v>0</v>
+      </c>
       <c r="G179" s="1">
         <v>45395</v>
       </c>
@@ -20244,6 +20922,9 @@
       <c r="D183">
         <v>31</v>
       </c>
+      <c r="E183">
+        <v>6500</v>
+      </c>
       <c r="F183">
         <v>250</v>
       </c>
@@ -20315,6 +20996,9 @@
       <c r="C184" t="s">
         <v>840</v>
       </c>
+      <c r="D184">
+        <v>33</v>
+      </c>
       <c r="E184">
         <v>6000</v>
       </c>
@@ -20332,6 +21016,9 @@
       </c>
       <c r="J184" t="s">
         <v>1729</v>
+      </c>
+      <c r="K184" t="s">
+        <v>1731</v>
       </c>
       <c r="L184">
         <v>0</v>
@@ -20398,6 +21085,9 @@
       <c r="E185">
         <v>5750</v>
       </c>
+      <c r="F185">
+        <v>0</v>
+      </c>
       <c r="G185" s="1">
         <v>43657</v>
       </c>
@@ -20481,6 +21171,12 @@
       <c r="D186">
         <v>19</v>
       </c>
+      <c r="E186">
+        <v>6500</v>
+      </c>
+      <c r="F186">
+        <v>0</v>
+      </c>
       <c r="G186" s="1">
         <v>45146</v>
       </c>
@@ -20552,14 +21248,23 @@
       <c r="C187" t="s">
         <v>840</v>
       </c>
+      <c r="D187">
+        <v>33</v>
+      </c>
       <c r="E187">
         <v>7500</v>
       </c>
+      <c r="F187">
+        <v>0</v>
+      </c>
       <c r="G187" s="1">
         <v>44084</v>
       </c>
       <c r="I187" t="s">
         <v>1331</v>
+      </c>
+      <c r="J187" t="s">
+        <v>1729</v>
       </c>
       <c r="K187" t="s">
         <v>1732</v>
@@ -20798,6 +21503,9 @@
       <c r="D190">
         <v>42</v>
       </c>
+      <c r="E190">
+        <v>6500</v>
+      </c>
       <c r="F190">
         <v>1000</v>
       </c>
@@ -20872,6 +21580,9 @@
       <c r="C191" t="s">
         <v>841</v>
       </c>
+      <c r="D191">
+        <v>33</v>
+      </c>
       <c r="E191">
         <v>6500</v>
       </c>
@@ -20958,6 +21669,9 @@
       <c r="E192">
         <v>6250</v>
       </c>
+      <c r="F192">
+        <v>0</v>
+      </c>
       <c r="G192" s="1">
         <v>45473</v>
       </c>
@@ -20966,6 +21680,12 @@
       </c>
       <c r="I192" t="s">
         <v>1450</v>
+      </c>
+      <c r="J192" t="s">
+        <v>1729</v>
+      </c>
+      <c r="K192" t="s">
+        <v>1731</v>
       </c>
       <c r="L192">
         <v>0</v>
@@ -21038,6 +21758,9 @@
       <c r="E193">
         <v>4800</v>
       </c>
+      <c r="F193">
+        <v>0</v>
+      </c>
       <c r="G193" s="1">
         <v>44330</v>
       </c>
@@ -21121,6 +21844,9 @@
       <c r="D194">
         <v>16</v>
       </c>
+      <c r="E194">
+        <v>6500</v>
+      </c>
       <c r="F194">
         <v>250</v>
       </c>
@@ -21135,6 +21861,9 @@
       </c>
       <c r="J194" t="s">
         <v>1728</v>
+      </c>
+      <c r="K194" t="s">
+        <v>1731</v>
       </c>
       <c r="L194">
         <v>0</v>
@@ -21189,8 +21918,14 @@
       <c r="C195" t="s">
         <v>843</v>
       </c>
+      <c r="D195">
+        <v>33</v>
+      </c>
       <c r="E195">
         <v>8000</v>
+      </c>
+      <c r="F195">
+        <v>0</v>
       </c>
       <c r="G195" s="1">
         <v>44800</v>
@@ -21281,6 +22016,9 @@
       <c r="I196" t="s">
         <v>1453</v>
       </c>
+      <c r="J196" t="s">
+        <v>1729</v>
+      </c>
       <c r="K196" t="s">
         <v>1731</v>
       </c>
@@ -21441,6 +22179,9 @@
       <c r="D198">
         <v>28</v>
       </c>
+      <c r="E198">
+        <v>6500</v>
+      </c>
       <c r="F198">
         <v>0</v>
       </c>
@@ -21455,6 +22196,9 @@
       </c>
       <c r="J198" t="s">
         <v>1729</v>
+      </c>
+      <c r="K198" t="s">
+        <v>1731</v>
       </c>
       <c r="L198">
         <v>0</v>
@@ -21684,11 +22428,20 @@
       <c r="D201">
         <v>30</v>
       </c>
+      <c r="E201">
+        <v>6500</v>
+      </c>
+      <c r="F201">
+        <v>0</v>
+      </c>
       <c r="G201" s="1">
         <v>45463</v>
       </c>
       <c r="H201" t="s">
         <v>1032</v>
+      </c>
+      <c r="J201" t="s">
+        <v>1729</v>
       </c>
       <c r="K201" t="s">
         <v>1731</v>
@@ -21749,8 +22502,14 @@
       <c r="C202" t="s">
         <v>841</v>
       </c>
+      <c r="D202">
+        <v>33</v>
+      </c>
       <c r="E202">
         <v>9750</v>
+      </c>
+      <c r="F202">
+        <v>0</v>
       </c>
       <c r="G202" s="1">
         <v>43976</v>
@@ -21832,6 +22591,9 @@
       <c r="E203">
         <v>6000</v>
       </c>
+      <c r="F203">
+        <v>0</v>
+      </c>
       <c r="G203" s="1">
         <v>44893</v>
       </c>
@@ -21915,6 +22677,9 @@
       <c r="E204">
         <v>-500</v>
       </c>
+      <c r="F204">
+        <v>0</v>
+      </c>
       <c r="H204" t="s">
         <v>1035</v>
       </c>
@@ -21923,6 +22688,9 @@
       </c>
       <c r="J204" t="s">
         <v>1728</v>
+      </c>
+      <c r="K204" t="s">
+        <v>1731</v>
       </c>
       <c r="L204">
         <v>0</v>
@@ -21989,6 +22757,9 @@
       <c r="C205" t="s">
         <v>842</v>
       </c>
+      <c r="D205">
+        <v>33</v>
+      </c>
       <c r="E205">
         <v>6800</v>
       </c>
@@ -22072,6 +22843,12 @@
       <c r="D206">
         <v>34</v>
       </c>
+      <c r="E206">
+        <v>6500</v>
+      </c>
+      <c r="F206">
+        <v>0</v>
+      </c>
       <c r="G206" s="1">
         <v>43520</v>
       </c>
@@ -22149,6 +22926,9 @@
       <c r="E207">
         <v>4500</v>
       </c>
+      <c r="F207">
+        <v>0</v>
+      </c>
       <c r="G207" s="1">
         <v>44341</v>
       </c>
@@ -22321,6 +23101,9 @@
       <c r="D209">
         <v>32</v>
       </c>
+      <c r="E209">
+        <v>6500</v>
+      </c>
       <c r="F209">
         <v>250</v>
       </c>
@@ -22332,6 +23115,9 @@
       </c>
       <c r="I209" t="s">
         <v>1463</v>
+      </c>
+      <c r="J209" t="s">
+        <v>1729</v>
       </c>
       <c r="K209" t="s">
         <v>1732</v>
@@ -22564,6 +23350,9 @@
       <c r="C212" t="s">
         <v>842</v>
       </c>
+      <c r="D212">
+        <v>33</v>
+      </c>
       <c r="E212">
         <v>5500</v>
       </c>
@@ -22644,6 +23433,9 @@
       <c r="D213">
         <v>36</v>
       </c>
+      <c r="E213">
+        <v>6500</v>
+      </c>
       <c r="F213">
         <v>500</v>
       </c>
@@ -22709,9 +23501,15 @@
       <c r="C214" t="s">
         <v>844</v>
       </c>
+      <c r="D214">
+        <v>33</v>
+      </c>
       <c r="E214">
         <v>9000</v>
       </c>
+      <c r="F214">
+        <v>0</v>
+      </c>
       <c r="G214" s="1">
         <v>45396</v>
       </c>
@@ -22720,6 +23518,9 @@
       </c>
       <c r="I214" t="s">
         <v>1467</v>
+      </c>
+      <c r="J214" t="s">
+        <v>1729</v>
       </c>
       <c r="K214" t="s">
         <v>1731</v>
@@ -22783,6 +23584,9 @@
       <c r="C215" t="s">
         <v>840</v>
       </c>
+      <c r="D215">
+        <v>33</v>
+      </c>
       <c r="E215">
         <v>6250</v>
       </c>
@@ -22866,6 +23670,9 @@
       <c r="D216">
         <v>40</v>
       </c>
+      <c r="E216">
+        <v>6500</v>
+      </c>
       <c r="F216">
         <v>250</v>
       </c>
@@ -22877,6 +23684,9 @@
       </c>
       <c r="I216" t="s">
         <v>1469</v>
+      </c>
+      <c r="J216" t="s">
+        <v>1729</v>
       </c>
       <c r="K216" t="s">
         <v>1732</v>
@@ -22955,6 +23765,12 @@
       <c r="I217" t="s">
         <v>1331</v>
       </c>
+      <c r="J217" t="s">
+        <v>1729</v>
+      </c>
+      <c r="K217" t="s">
+        <v>1731</v>
+      </c>
       <c r="L217">
         <v>0</v>
       </c>
@@ -23127,6 +23943,9 @@
       <c r="I219" t="s">
         <v>1471</v>
       </c>
+      <c r="J219" t="s">
+        <v>1729</v>
+      </c>
       <c r="K219" t="s">
         <v>1732</v>
       </c>
@@ -23213,6 +24032,9 @@
       <c r="J220" t="s">
         <v>1728</v>
       </c>
+      <c r="K220" t="s">
+        <v>1731</v>
+      </c>
       <c r="L220">
         <v>0</v>
       </c>
@@ -23278,6 +24100,9 @@
       <c r="C221" t="s">
         <v>841</v>
       </c>
+      <c r="D221">
+        <v>33</v>
+      </c>
       <c r="E221">
         <v>8000</v>
       </c>
@@ -23361,6 +24186,9 @@
       <c r="D222">
         <v>34</v>
       </c>
+      <c r="E222">
+        <v>6500</v>
+      </c>
       <c r="F222">
         <v>300</v>
       </c>
@@ -23372,6 +24200,12 @@
       </c>
       <c r="I222" t="s">
         <v>1474</v>
+      </c>
+      <c r="J222" t="s">
+        <v>1729</v>
+      </c>
+      <c r="K222" t="s">
+        <v>1731</v>
       </c>
       <c r="L222">
         <v>0</v>
@@ -23435,6 +24269,9 @@
       <c r="E223">
         <v>5500</v>
       </c>
+      <c r="F223">
+        <v>0</v>
+      </c>
       <c r="G223" s="1">
         <v>45386</v>
       </c>
@@ -23521,6 +24358,9 @@
       <c r="E224">
         <v>9500</v>
       </c>
+      <c r="F224">
+        <v>0</v>
+      </c>
       <c r="G224" s="1">
         <v>44921</v>
       </c>
@@ -23601,6 +24441,15 @@
       <c r="C225" t="s">
         <v>843</v>
       </c>
+      <c r="D225">
+        <v>33</v>
+      </c>
+      <c r="E225">
+        <v>6500</v>
+      </c>
+      <c r="F225">
+        <v>0</v>
+      </c>
       <c r="G225" s="1">
         <v>43843</v>
       </c>
@@ -23684,6 +24533,9 @@
       <c r="I226" t="s">
         <v>1477</v>
       </c>
+      <c r="J226" t="s">
+        <v>1729</v>
+      </c>
       <c r="K226" t="s">
         <v>1731</v>
       </c>
@@ -23767,6 +24619,9 @@
       <c r="H227" t="s">
         <v>1052</v>
       </c>
+      <c r="J227" t="s">
+        <v>1729</v>
+      </c>
       <c r="K227" t="s">
         <v>1732</v>
       </c>
@@ -23924,6 +24779,9 @@
       <c r="D229">
         <v>42</v>
       </c>
+      <c r="E229">
+        <v>6500</v>
+      </c>
       <c r="F229">
         <v>300</v>
       </c>
@@ -23938,6 +24796,9 @@
       </c>
       <c r="J229" t="s">
         <v>1729</v>
+      </c>
+      <c r="K229" t="s">
+        <v>1731</v>
       </c>
       <c r="L229">
         <v>0</v>
@@ -23992,6 +24853,9 @@
       <c r="C230" t="s">
         <v>844</v>
       </c>
+      <c r="D230">
+        <v>33</v>
+      </c>
       <c r="E230">
         <v>6500</v>
       </c>
@@ -24078,6 +24942,9 @@
       <c r="E231">
         <v>8200</v>
       </c>
+      <c r="F231">
+        <v>0</v>
+      </c>
       <c r="G231" s="1">
         <v>45165</v>
       </c>
@@ -24161,6 +25028,12 @@
       <c r="D232">
         <v>35</v>
       </c>
+      <c r="E232">
+        <v>6500</v>
+      </c>
+      <c r="F232">
+        <v>0</v>
+      </c>
       <c r="G232" s="1">
         <v>44577</v>
       </c>
@@ -24238,6 +25111,9 @@
       <c r="E233">
         <v>5250</v>
       </c>
+      <c r="F233">
+        <v>0</v>
+      </c>
       <c r="G233" s="1">
         <v>44424</v>
       </c>
@@ -24246,6 +25122,9 @@
       </c>
       <c r="I233" t="s">
         <v>1483</v>
+      </c>
+      <c r="J233" t="s">
+        <v>1729</v>
       </c>
       <c r="K233" t="s">
         <v>1732</v>
@@ -24404,6 +25283,9 @@
       <c r="C235" t="s">
         <v>841</v>
       </c>
+      <c r="D235">
+        <v>33</v>
+      </c>
       <c r="E235">
         <v>9000</v>
       </c>
@@ -24421,6 +25303,9 @@
       </c>
       <c r="J235" t="s">
         <v>1730</v>
+      </c>
+      <c r="K235" t="s">
+        <v>1731</v>
       </c>
       <c r="L235">
         <v>0</v>
@@ -24484,6 +25369,12 @@
       <c r="D236">
         <v>39</v>
       </c>
+      <c r="E236">
+        <v>6500</v>
+      </c>
+      <c r="F236">
+        <v>0</v>
+      </c>
       <c r="H236" t="s">
         <v>1060</v>
       </c>
@@ -24552,6 +25443,9 @@
       <c r="C237" t="s">
         <v>845</v>
       </c>
+      <c r="D237">
+        <v>33</v>
+      </c>
       <c r="E237">
         <v>6500</v>
       </c>
@@ -24718,8 +25612,14 @@
       <c r="C239" t="s">
         <v>844</v>
       </c>
+      <c r="D239">
+        <v>33</v>
+      </c>
       <c r="E239">
         <v>-1000</v>
+      </c>
+      <c r="F239">
+        <v>0</v>
       </c>
       <c r="G239" s="1">
         <v>43832</v>
@@ -24798,6 +25698,9 @@
       <c r="D240">
         <v>41</v>
       </c>
+      <c r="E240">
+        <v>6500</v>
+      </c>
       <c r="F240">
         <v>750</v>
       </c>
@@ -24878,6 +25781,9 @@
       <c r="E241">
         <v>6000</v>
       </c>
+      <c r="F241">
+        <v>0</v>
+      </c>
       <c r="G241" s="1">
         <v>43635</v>
       </c>
@@ -24961,6 +25867,9 @@
       <c r="E242">
         <v>7200</v>
       </c>
+      <c r="F242">
+        <v>0</v>
+      </c>
       <c r="G242" s="1">
         <v>43713</v>
       </c>
@@ -25047,6 +25956,9 @@
       <c r="E243">
         <v>5500</v>
       </c>
+      <c r="F243">
+        <v>0</v>
+      </c>
       <c r="G243" s="1">
         <v>45399</v>
       </c>
@@ -25127,6 +26039,9 @@
       <c r="D244">
         <v>36</v>
       </c>
+      <c r="E244">
+        <v>6500</v>
+      </c>
       <c r="F244">
         <v>250</v>
       </c>
@@ -25204,11 +26119,17 @@
       <c r="E245">
         <v>8500</v>
       </c>
+      <c r="F245">
+        <v>0</v>
+      </c>
       <c r="G245" s="1">
         <v>45429</v>
       </c>
       <c r="I245" t="s">
         <v>1494</v>
+      </c>
+      <c r="J245" t="s">
+        <v>1729</v>
       </c>
       <c r="K245" t="s">
         <v>1731</v>
@@ -25290,6 +26211,9 @@
       <c r="I246" t="s">
         <v>1495</v>
       </c>
+      <c r="J246" t="s">
+        <v>1729</v>
+      </c>
       <c r="K246" t="s">
         <v>1732</v>
       </c>
@@ -25358,6 +26282,12 @@
       <c r="C247" t="s">
         <v>844</v>
       </c>
+      <c r="D247">
+        <v>33</v>
+      </c>
+      <c r="E247">
+        <v>6500</v>
+      </c>
       <c r="F247">
         <v>750</v>
       </c>
@@ -25515,6 +26445,9 @@
       <c r="C249" t="s">
         <v>843</v>
       </c>
+      <c r="D249">
+        <v>33</v>
+      </c>
       <c r="E249">
         <v>6200</v>
       </c>
@@ -25613,6 +26546,12 @@
       <c r="I250" t="s">
         <v>1499</v>
       </c>
+      <c r="J250" t="s">
+        <v>1729</v>
+      </c>
+      <c r="K250" t="s">
+        <v>1731</v>
+      </c>
       <c r="L250">
         <v>0</v>
       </c>
@@ -25681,6 +26620,9 @@
       <c r="D251">
         <v>38</v>
       </c>
+      <c r="E251">
+        <v>6500</v>
+      </c>
       <c r="F251">
         <v>-50</v>
       </c>
@@ -25930,6 +26872,9 @@
       <c r="D254">
         <v>47</v>
       </c>
+      <c r="E254">
+        <v>6500</v>
+      </c>
       <c r="F254">
         <v>0</v>
       </c>
@@ -26019,6 +26964,12 @@
       <c r="I255" t="s">
         <v>1503</v>
       </c>
+      <c r="J255" t="s">
+        <v>1729</v>
+      </c>
+      <c r="K255" t="s">
+        <v>1731</v>
+      </c>
       <c r="L255">
         <v>0</v>
       </c>
@@ -26081,6 +27032,9 @@
       <c r="C256" t="s">
         <v>844</v>
       </c>
+      <c r="D256">
+        <v>33</v>
+      </c>
       <c r="E256">
         <v>8000</v>
       </c>
@@ -26095,6 +27049,9 @@
       </c>
       <c r="I256" t="s">
         <v>1504</v>
+      </c>
+      <c r="J256" t="s">
+        <v>1729</v>
       </c>
       <c r="K256" t="s">
         <v>1731</v>
@@ -26158,6 +27115,9 @@
       <c r="C257" t="s">
         <v>842</v>
       </c>
+      <c r="D257">
+        <v>33</v>
+      </c>
       <c r="E257">
         <v>-250</v>
       </c>
@@ -26327,6 +27287,9 @@
       <c r="D259">
         <v>29</v>
       </c>
+      <c r="E259">
+        <v>6500</v>
+      </c>
       <c r="F259">
         <v>1250</v>
       </c>
@@ -26407,6 +27370,9 @@
       <c r="E260">
         <v>4500</v>
       </c>
+      <c r="F260">
+        <v>0</v>
+      </c>
       <c r="G260" s="1">
         <v>44788</v>
       </c>
@@ -26487,6 +27453,9 @@
       <c r="C261" t="s">
         <v>842</v>
       </c>
+      <c r="D261">
+        <v>33</v>
+      </c>
       <c r="E261">
         <v>7200</v>
       </c>
@@ -26570,6 +27539,9 @@
       <c r="D262">
         <v>21</v>
       </c>
+      <c r="E262">
+        <v>6500</v>
+      </c>
       <c r="F262">
         <v>500</v>
       </c>
@@ -26584,6 +27556,9 @@
       </c>
       <c r="J262" t="s">
         <v>1729</v>
+      </c>
+      <c r="K262" t="s">
+        <v>1731</v>
       </c>
       <c r="L262">
         <v>0</v>
@@ -26647,6 +27622,9 @@
       <c r="E263">
         <v>9250</v>
       </c>
+      <c r="F263">
+        <v>0</v>
+      </c>
       <c r="G263" s="1">
         <v>44575</v>
       </c>
@@ -26721,6 +27699,9 @@
       <c r="C264" t="s">
         <v>844</v>
       </c>
+      <c r="D264">
+        <v>33</v>
+      </c>
       <c r="E264">
         <v>5500</v>
       </c>
@@ -26804,6 +27785,9 @@
       <c r="E265">
         <v>6500</v>
       </c>
+      <c r="F265">
+        <v>0</v>
+      </c>
       <c r="G265" s="1">
         <v>44790</v>
       </c>
@@ -26812,6 +27796,12 @@
       </c>
       <c r="I265" t="s">
         <v>1512</v>
+      </c>
+      <c r="J265" t="s">
+        <v>1729</v>
+      </c>
+      <c r="K265" t="s">
+        <v>1731</v>
       </c>
       <c r="L265">
         <v>0</v>
@@ -26878,6 +27868,9 @@
       <c r="D266">
         <v>27</v>
       </c>
+      <c r="E266">
+        <v>6500</v>
+      </c>
       <c r="F266">
         <v>750</v>
       </c>
@@ -27130,6 +28123,12 @@
       <c r="D269">
         <v>24</v>
       </c>
+      <c r="E269">
+        <v>6500</v>
+      </c>
+      <c r="F269">
+        <v>0</v>
+      </c>
       <c r="G269" s="1">
         <v>44063</v>
       </c>
@@ -27201,9 +28200,15 @@
       <c r="C270" t="s">
         <v>841</v>
       </c>
+      <c r="D270">
+        <v>33</v>
+      </c>
       <c r="E270">
         <v>6200</v>
       </c>
+      <c r="F270">
+        <v>0</v>
+      </c>
       <c r="G270" s="1">
         <v>45028</v>
       </c>
@@ -27215,6 +28220,9 @@
       </c>
       <c r="J270" t="s">
         <v>1728</v>
+      </c>
+      <c r="K270" t="s">
+        <v>1731</v>
       </c>
       <c r="L270">
         <v>1</v>
@@ -27364,6 +28372,9 @@
       <c r="C272" t="s">
         <v>845</v>
       </c>
+      <c r="D272">
+        <v>33</v>
+      </c>
       <c r="E272">
         <v>4800</v>
       </c>
@@ -27381,6 +28392,9 @@
       </c>
       <c r="J272" t="s">
         <v>1728</v>
+      </c>
+      <c r="K272" t="s">
+        <v>1731</v>
       </c>
       <c r="L272">
         <v>1</v>
@@ -27444,6 +28458,12 @@
       <c r="D273">
         <v>33</v>
       </c>
+      <c r="E273">
+        <v>6500</v>
+      </c>
+      <c r="F273">
+        <v>0</v>
+      </c>
       <c r="G273" s="1">
         <v>44086</v>
       </c>
@@ -27714,6 +28734,9 @@
       <c r="J276" t="s">
         <v>1729</v>
       </c>
+      <c r="K276" t="s">
+        <v>1731</v>
+      </c>
       <c r="L276">
         <v>0</v>
       </c>
@@ -27782,6 +28805,9 @@
       <c r="D277">
         <v>35</v>
       </c>
+      <c r="E277">
+        <v>6500</v>
+      </c>
       <c r="F277">
         <v>250</v>
       </c>
@@ -27874,6 +28900,9 @@
       <c r="J278" t="s">
         <v>1729</v>
       </c>
+      <c r="K278" t="s">
+        <v>1731</v>
+      </c>
       <c r="L278">
         <v>0</v>
       </c>
@@ -27936,6 +28965,9 @@
       <c r="C279" t="s">
         <v>842</v>
       </c>
+      <c r="D279">
+        <v>33</v>
+      </c>
       <c r="E279">
         <v>7200</v>
       </c>
@@ -28022,6 +29054,9 @@
       <c r="E280">
         <v>6250</v>
       </c>
+      <c r="F280">
+        <v>0</v>
+      </c>
       <c r="G280" s="1">
         <v>45037</v>
       </c>
@@ -28102,6 +29137,12 @@
       <c r="C281" t="s">
         <v>844</v>
       </c>
+      <c r="D281">
+        <v>33</v>
+      </c>
+      <c r="E281">
+        <v>6500</v>
+      </c>
       <c r="F281">
         <v>-50</v>
       </c>
@@ -28262,6 +29303,9 @@
       <c r="D283">
         <v>-3</v>
       </c>
+      <c r="E283">
+        <v>6500</v>
+      </c>
       <c r="F283">
         <v>250</v>
       </c>
@@ -28273,6 +29317,9 @@
       </c>
       <c r="I283" t="s">
         <v>1529</v>
+      </c>
+      <c r="J283" t="s">
+        <v>1729</v>
       </c>
       <c r="K283" t="s">
         <v>1731</v>
@@ -28514,6 +29561,9 @@
       <c r="E286">
         <v>8200</v>
       </c>
+      <c r="F286">
+        <v>0</v>
+      </c>
       <c r="G286" s="1">
         <v>45524</v>
       </c>
@@ -28612,6 +29662,12 @@
       <c r="I287" t="s">
         <v>1533</v>
       </c>
+      <c r="J287" t="s">
+        <v>1729</v>
+      </c>
+      <c r="K287" t="s">
+        <v>1731</v>
+      </c>
       <c r="L287">
         <v>0</v>
       </c>
@@ -28677,6 +29733,12 @@
       <c r="C288" t="s">
         <v>840</v>
       </c>
+      <c r="D288">
+        <v>33</v>
+      </c>
+      <c r="E288">
+        <v>6500</v>
+      </c>
       <c r="F288">
         <v>500</v>
       </c>
@@ -28688,6 +29750,9 @@
       </c>
       <c r="I288" t="s">
         <v>1534</v>
+      </c>
+      <c r="J288" t="s">
+        <v>1729</v>
       </c>
       <c r="K288" t="s">
         <v>1732</v>
@@ -28742,9 +29807,15 @@
       <c r="C289" t="s">
         <v>844</v>
       </c>
+      <c r="D289">
+        <v>33</v>
+      </c>
       <c r="E289">
         <v>6500</v>
       </c>
+      <c r="F289">
+        <v>0</v>
+      </c>
       <c r="G289" s="1">
         <v>43749</v>
       </c>
@@ -28756,6 +29827,9 @@
       </c>
       <c r="J289" t="s">
         <v>1729</v>
+      </c>
+      <c r="K289" t="s">
+        <v>1731</v>
       </c>
       <c r="L289">
         <v>0</v>
@@ -28816,6 +29890,9 @@
       <c r="D290">
         <v>34</v>
       </c>
+      <c r="E290">
+        <v>6500</v>
+      </c>
       <c r="F290">
         <v>250</v>
       </c>
@@ -28896,6 +29973,9 @@
       <c r="E291">
         <v>7500</v>
       </c>
+      <c r="F291">
+        <v>0</v>
+      </c>
       <c r="H291" t="s">
         <v>1107</v>
       </c>
@@ -28979,6 +30059,9 @@
       <c r="E292">
         <v>5250</v>
       </c>
+      <c r="F292">
+        <v>0</v>
+      </c>
       <c r="H292" t="s">
         <v>1108</v>
       </c>
@@ -29056,6 +30139,9 @@
       <c r="C293" t="s">
         <v>843</v>
       </c>
+      <c r="D293">
+        <v>33</v>
+      </c>
       <c r="E293">
         <v>-5000</v>
       </c>
@@ -29070,6 +30156,12 @@
       </c>
       <c r="I293" t="s">
         <v>1539</v>
+      </c>
+      <c r="J293" t="s">
+        <v>1729</v>
+      </c>
+      <c r="K293" t="s">
+        <v>1731</v>
       </c>
       <c r="L293">
         <v>1</v>
@@ -29151,6 +30243,9 @@
       <c r="J294" t="s">
         <v>1728</v>
       </c>
+      <c r="K294" t="s">
+        <v>1731</v>
+      </c>
       <c r="L294">
         <v>0</v>
       </c>
@@ -29216,6 +30311,12 @@
       <c r="C295" t="s">
         <v>840</v>
       </c>
+      <c r="D295">
+        <v>33</v>
+      </c>
+      <c r="E295">
+        <v>6500</v>
+      </c>
       <c r="F295">
         <v>250</v>
       </c>
@@ -29227,6 +30328,9 @@
       </c>
       <c r="I295" t="s">
         <v>1331</v>
+      </c>
+      <c r="J295" t="s">
+        <v>1729</v>
       </c>
       <c r="K295" t="s">
         <v>1732</v>
@@ -29287,6 +30391,9 @@
       <c r="E296">
         <v>9000</v>
       </c>
+      <c r="F296">
+        <v>0</v>
+      </c>
       <c r="G296" s="1">
         <v>45374</v>
       </c>
@@ -29373,6 +30480,9 @@
       <c r="E297">
         <v>4500</v>
       </c>
+      <c r="F297">
+        <v>0</v>
+      </c>
       <c r="G297" s="1">
         <v>45063</v>
       </c>
@@ -29456,6 +30566,12 @@
       <c r="D298">
         <v>36</v>
       </c>
+      <c r="E298">
+        <v>6500</v>
+      </c>
+      <c r="F298">
+        <v>0</v>
+      </c>
       <c r="G298" s="1">
         <v>44575</v>
       </c>
@@ -29533,6 +30649,9 @@
       <c r="E299">
         <v>7200</v>
       </c>
+      <c r="F299">
+        <v>0</v>
+      </c>
       <c r="G299" s="1">
         <v>45263</v>
       </c>
@@ -29544,6 +30663,9 @@
       </c>
       <c r="J299" t="s">
         <v>1729</v>
+      </c>
+      <c r="K299" t="s">
+        <v>1731</v>
       </c>
       <c r="L299">
         <v>0</v>
@@ -29628,6 +30750,9 @@
       <c r="J300" t="s">
         <v>1728</v>
       </c>
+      <c r="K300" t="s">
+        <v>1731</v>
+      </c>
       <c r="L300">
         <v>0</v>
       </c>
@@ -29690,9 +30815,15 @@
       <c r="C301" t="s">
         <v>840</v>
       </c>
+      <c r="D301">
+        <v>33</v>
+      </c>
       <c r="E301">
         <v>6750</v>
       </c>
+      <c r="F301">
+        <v>0</v>
+      </c>
       <c r="G301" s="1">
         <v>43842</v>
       </c>
@@ -29704,6 +30835,9 @@
       </c>
       <c r="J301" t="s">
         <v>1728</v>
+      </c>
+      <c r="K301" t="s">
+        <v>1731</v>
       </c>
       <c r="L301">
         <v>1</v>
@@ -29767,6 +30901,9 @@
       <c r="D302">
         <v>25</v>
       </c>
+      <c r="E302">
+        <v>6500</v>
+      </c>
       <c r="F302">
         <v>500</v>
       </c>
@@ -29778,6 +30915,9 @@
       </c>
       <c r="I302" t="s">
         <v>1547</v>
+      </c>
+      <c r="J302" t="s">
+        <v>1729</v>
       </c>
       <c r="K302" t="s">
         <v>1731</v>
@@ -29838,8 +30978,14 @@
       <c r="C303" t="s">
         <v>843</v>
       </c>
+      <c r="D303">
+        <v>33</v>
+      </c>
       <c r="E303">
         <v>8000</v>
+      </c>
+      <c r="F303">
+        <v>0</v>
       </c>
       <c r="G303" s="1">
         <v>43566</v>
@@ -29930,6 +31076,9 @@
       <c r="I304" t="s">
         <v>1548</v>
       </c>
+      <c r="J304" t="s">
+        <v>1729</v>
+      </c>
       <c r="K304" t="s">
         <v>1732</v>
       </c>
@@ -30001,6 +31150,12 @@
       <c r="D305">
         <v>46</v>
       </c>
+      <c r="E305">
+        <v>6500</v>
+      </c>
+      <c r="F305">
+        <v>0</v>
+      </c>
       <c r="G305" s="1">
         <v>45444</v>
       </c>
@@ -30012,6 +31167,9 @@
       </c>
       <c r="J305" t="s">
         <v>1728</v>
+      </c>
+      <c r="K305" t="s">
+        <v>1731</v>
       </c>
       <c r="L305">
         <v>0</v>
@@ -30075,6 +31233,9 @@
       <c r="E306">
         <v>6500</v>
       </c>
+      <c r="F306">
+        <v>0</v>
+      </c>
       <c r="G306" s="1">
         <v>44459</v>
       </c>
@@ -30086,6 +31247,9 @@
       </c>
       <c r="J306" t="s">
         <v>1729</v>
+      </c>
+      <c r="K306" t="s">
+        <v>1731</v>
       </c>
       <c r="L306">
         <v>0</v>
@@ -30330,6 +31494,9 @@
       <c r="D309">
         <v>22</v>
       </c>
+      <c r="E309">
+        <v>6500</v>
+      </c>
       <c r="F309">
         <v>500</v>
       </c>
@@ -30344,6 +31511,9 @@
       </c>
       <c r="J309" t="s">
         <v>1729</v>
+      </c>
+      <c r="K309" t="s">
+        <v>1731</v>
       </c>
       <c r="L309">
         <v>0</v>
@@ -30422,6 +31592,9 @@
       <c r="J310" t="s">
         <v>1729</v>
       </c>
+      <c r="K310" t="s">
+        <v>1731</v>
+      </c>
       <c r="L310">
         <v>0</v>
       </c>
@@ -30487,6 +31660,9 @@
       <c r="C311" t="s">
         <v>840</v>
       </c>
+      <c r="D311">
+        <v>33</v>
+      </c>
       <c r="E311">
         <v>6200</v>
       </c>
@@ -30561,6 +31737,12 @@
       <c r="C312" t="s">
         <v>844</v>
       </c>
+      <c r="D312">
+        <v>33</v>
+      </c>
+      <c r="E312">
+        <v>6500</v>
+      </c>
       <c r="F312">
         <v>750</v>
       </c>
@@ -30635,6 +31817,9 @@
       <c r="E313">
         <v>5750</v>
       </c>
+      <c r="F313">
+        <v>0</v>
+      </c>
       <c r="G313" s="1">
         <v>45001</v>
       </c>
@@ -30715,6 +31900,9 @@
       <c r="C314" t="s">
         <v>842</v>
       </c>
+      <c r="D314">
+        <v>33</v>
+      </c>
       <c r="E314">
         <v>9000</v>
       </c>
@@ -30798,6 +31986,9 @@
       <c r="E315">
         <v>-2000</v>
       </c>
+      <c r="F315">
+        <v>0</v>
+      </c>
       <c r="G315" s="1">
         <v>45108</v>
       </c>
@@ -30884,6 +32075,9 @@
       <c r="E316">
         <v>6500</v>
       </c>
+      <c r="F316">
+        <v>0</v>
+      </c>
       <c r="G316" s="1">
         <v>44792</v>
       </c>
@@ -30967,6 +32161,9 @@
       <c r="D317">
         <v>38</v>
       </c>
+      <c r="E317">
+        <v>6500</v>
+      </c>
       <c r="F317">
         <v>750</v>
       </c>
@@ -31041,8 +32238,14 @@
       <c r="C318" t="s">
         <v>840</v>
       </c>
+      <c r="D318">
+        <v>33</v>
+      </c>
       <c r="E318">
         <v>7200</v>
+      </c>
+      <c r="F318">
+        <v>0</v>
       </c>
       <c r="G318" s="1">
         <v>44764</v>
@@ -31204,6 +32407,12 @@
       <c r="D320">
         <v>30</v>
       </c>
+      <c r="E320">
+        <v>6500</v>
+      </c>
+      <c r="F320">
+        <v>0</v>
+      </c>
       <c r="G320" s="1">
         <v>44905</v>
       </c>
@@ -31293,6 +32502,12 @@
       <c r="I321" t="s">
         <v>1564</v>
       </c>
+      <c r="J321" t="s">
+        <v>1729</v>
+      </c>
+      <c r="K321" t="s">
+        <v>1731</v>
+      </c>
       <c r="L321">
         <v>0</v>
       </c>
@@ -31361,6 +32576,9 @@
       <c r="E322">
         <v>5500</v>
       </c>
+      <c r="F322">
+        <v>0</v>
+      </c>
       <c r="G322" s="1">
         <v>45050</v>
       </c>
@@ -31438,6 +32656,9 @@
       <c r="C323" t="s">
         <v>840</v>
       </c>
+      <c r="D323">
+        <v>33</v>
+      </c>
       <c r="E323">
         <v>7500</v>
       </c>
@@ -31452,6 +32673,12 @@
       </c>
       <c r="I323" t="s">
         <v>1566</v>
+      </c>
+      <c r="J323" t="s">
+        <v>1729</v>
+      </c>
+      <c r="K323" t="s">
+        <v>1731</v>
       </c>
       <c r="L323">
         <v>1</v>
@@ -31515,6 +32742,12 @@
       <c r="D324">
         <v>34</v>
       </c>
+      <c r="E324">
+        <v>6500</v>
+      </c>
+      <c r="F324">
+        <v>0</v>
+      </c>
       <c r="G324" s="1">
         <v>44889</v>
       </c>
@@ -31523,6 +32756,9 @@
       </c>
       <c r="I324" t="s">
         <v>1567</v>
+      </c>
+      <c r="J324" t="s">
+        <v>1729</v>
       </c>
       <c r="K324" t="s">
         <v>1731</v>
@@ -31583,6 +32819,9 @@
       <c r="C325" t="s">
         <v>841</v>
       </c>
+      <c r="D325">
+        <v>33</v>
+      </c>
       <c r="E325">
         <v>6500</v>
       </c>
@@ -31597,6 +32836,9 @@
       </c>
       <c r="I325" t="s">
         <v>1568</v>
+      </c>
+      <c r="J325" t="s">
+        <v>1729</v>
       </c>
       <c r="K325" t="s">
         <v>1732</v>
@@ -31663,6 +32905,12 @@
       <c r="D326">
         <v>175</v>
       </c>
+      <c r="E326">
+        <v>6500</v>
+      </c>
+      <c r="F326">
+        <v>0</v>
+      </c>
       <c r="G326" s="1">
         <v>44006</v>
       </c>
@@ -31671,6 +32919,9 @@
       </c>
       <c r="I326" t="s">
         <v>1569</v>
+      </c>
+      <c r="J326" t="s">
+        <v>1729</v>
       </c>
       <c r="K326" t="s">
         <v>1731</v>
@@ -31823,6 +33074,9 @@
       <c r="E328">
         <v>4800</v>
       </c>
+      <c r="F328">
+        <v>0</v>
+      </c>
       <c r="G328" s="1">
         <v>43662</v>
       </c>
@@ -31909,6 +33163,9 @@
       <c r="E329">
         <v>6250</v>
       </c>
+      <c r="F329">
+        <v>0</v>
+      </c>
       <c r="G329" s="1">
         <v>44057</v>
       </c>
@@ -31917,6 +33174,12 @@
       </c>
       <c r="I329" t="s">
         <v>1572</v>
+      </c>
+      <c r="J329" t="s">
+        <v>1729</v>
+      </c>
+      <c r="K329" t="s">
+        <v>1731</v>
       </c>
       <c r="L329">
         <v>0</v>
@@ -31983,6 +33246,9 @@
       <c r="C330" t="s">
         <v>842</v>
       </c>
+      <c r="D330">
+        <v>33</v>
+      </c>
       <c r="E330">
         <v>-750</v>
       </c>
@@ -31997,6 +33263,9 @@
       </c>
       <c r="I330" t="s">
         <v>1573</v>
+      </c>
+      <c r="J330" t="s">
+        <v>1729</v>
       </c>
       <c r="K330" t="s">
         <v>1732</v>
@@ -32063,6 +33332,9 @@
       <c r="D331">
         <v>37</v>
       </c>
+      <c r="E331">
+        <v>6500</v>
+      </c>
       <c r="F331">
         <v>-200</v>
       </c>
@@ -32137,6 +33409,9 @@
       <c r="C332" t="s">
         <v>842</v>
       </c>
+      <c r="D332">
+        <v>33</v>
+      </c>
       <c r="E332">
         <v>5500</v>
       </c>
@@ -32306,6 +33581,9 @@
       <c r="D334">
         <v>29</v>
       </c>
+      <c r="E334">
+        <v>6500</v>
+      </c>
       <c r="F334">
         <v>250</v>
       </c>
@@ -32380,9 +33658,15 @@
       <c r="C335" t="s">
         <v>844</v>
       </c>
+      <c r="D335">
+        <v>33</v>
+      </c>
       <c r="E335">
         <v>8250</v>
       </c>
+      <c r="F335">
+        <v>0</v>
+      </c>
       <c r="G335" s="1">
         <v>44550</v>
       </c>
@@ -32391,6 +33675,9 @@
       </c>
       <c r="J335" t="s">
         <v>1730</v>
+      </c>
+      <c r="K335" t="s">
+        <v>1731</v>
       </c>
       <c r="L335">
         <v>1</v>
@@ -32555,6 +33842,9 @@
       <c r="I337" t="s">
         <v>1579</v>
       </c>
+      <c r="J337" t="s">
+        <v>1729</v>
+      </c>
       <c r="K337" t="s">
         <v>1731</v>
       </c>
@@ -32623,6 +33913,12 @@
       <c r="C338" t="s">
         <v>842</v>
       </c>
+      <c r="D338">
+        <v>33</v>
+      </c>
+      <c r="E338">
+        <v>6500</v>
+      </c>
       <c r="F338">
         <v>500</v>
       </c>
@@ -32637,6 +33933,9 @@
       </c>
       <c r="J338" t="s">
         <v>1728</v>
+      </c>
+      <c r="K338" t="s">
+        <v>1731</v>
       </c>
       <c r="L338">
         <v>1</v>
@@ -32706,6 +34005,9 @@
       <c r="I339" t="s">
         <v>1581</v>
       </c>
+      <c r="J339" t="s">
+        <v>1729</v>
+      </c>
       <c r="K339" t="s">
         <v>1731</v>
       </c>
@@ -32780,6 +34082,9 @@
       <c r="E340">
         <v>6800</v>
       </c>
+      <c r="F340">
+        <v>0</v>
+      </c>
       <c r="G340" s="1">
         <v>45590</v>
       </c>
@@ -32791,6 +34096,9 @@
       </c>
       <c r="J340" t="s">
         <v>1729</v>
+      </c>
+      <c r="K340" t="s">
+        <v>1731</v>
       </c>
       <c r="L340">
         <v>0</v>
@@ -32860,6 +34168,9 @@
       <c r="D341">
         <v>-2</v>
       </c>
+      <c r="E341">
+        <v>6500</v>
+      </c>
       <c r="F341">
         <v>-50</v>
       </c>
@@ -32937,6 +34248,9 @@
       <c r="E342">
         <v>5200</v>
       </c>
+      <c r="F342">
+        <v>0</v>
+      </c>
       <c r="H342" t="s">
         <v>1154</v>
       </c>
@@ -33032,6 +34346,9 @@
       <c r="I343" t="s">
         <v>1585</v>
       </c>
+      <c r="J343" t="s">
+        <v>1729</v>
+      </c>
       <c r="K343" t="s">
         <v>1732</v>
       </c>
@@ -33100,8 +34417,14 @@
       <c r="C344" t="s">
         <v>842</v>
       </c>
+      <c r="D344">
+        <v>33</v>
+      </c>
       <c r="E344">
         <v>6500</v>
+      </c>
+      <c r="F344">
+        <v>0</v>
       </c>
       <c r="G344" s="1">
         <v>45504</v>
@@ -33174,6 +34497,12 @@
       <c r="C345" t="s">
         <v>840</v>
       </c>
+      <c r="D345">
+        <v>33</v>
+      </c>
+      <c r="E345">
+        <v>6500</v>
+      </c>
       <c r="F345">
         <v>500</v>
       </c>
@@ -33188,6 +34517,9 @@
       </c>
       <c r="J345" t="s">
         <v>1728</v>
+      </c>
+      <c r="K345" t="s">
+        <v>1731</v>
       </c>
       <c r="L345">
         <v>1</v>
@@ -33245,6 +34577,9 @@
       <c r="E346">
         <v>5250</v>
       </c>
+      <c r="F346">
+        <v>0</v>
+      </c>
       <c r="G346" s="1">
         <v>44935</v>
       </c>
@@ -33343,6 +34678,12 @@
       <c r="I347" t="s">
         <v>1589</v>
       </c>
+      <c r="J347" t="s">
+        <v>1729</v>
+      </c>
+      <c r="K347" t="s">
+        <v>1731</v>
+      </c>
       <c r="L347">
         <v>0</v>
       </c>
@@ -33500,6 +34841,9 @@
       <c r="D349">
         <v>155</v>
       </c>
+      <c r="E349">
+        <v>6500</v>
+      </c>
       <c r="F349">
         <v>-50</v>
       </c>
@@ -33514,6 +34858,9 @@
       </c>
       <c r="J349" t="s">
         <v>1729</v>
+      </c>
+      <c r="K349" t="s">
+        <v>1731</v>
       </c>
       <c r="L349">
         <v>0</v>
@@ -33574,6 +34921,9 @@
       <c r="E350">
         <v>7200</v>
       </c>
+      <c r="F350">
+        <v>0</v>
+      </c>
       <c r="G350" s="1">
         <v>45516</v>
       </c>
@@ -33654,6 +35004,9 @@
       <c r="E351">
         <v>5500</v>
       </c>
+      <c r="F351">
+        <v>0</v>
+      </c>
       <c r="G351" s="1">
         <v>45603</v>
       </c>
@@ -33731,8 +35084,14 @@
       <c r="C352" t="s">
         <v>840</v>
       </c>
+      <c r="D352">
+        <v>33</v>
+      </c>
       <c r="E352">
         <v>6500</v>
+      </c>
+      <c r="F352">
+        <v>0</v>
       </c>
       <c r="G352" s="1">
         <v>43508</v>
@@ -33811,6 +35170,9 @@
       <c r="D353">
         <v>30</v>
       </c>
+      <c r="E353">
+        <v>6500</v>
+      </c>
       <c r="F353">
         <v>1000</v>
       </c>
@@ -33819,6 +35181,9 @@
       </c>
       <c r="J353" t="s">
         <v>1729</v>
+      </c>
+      <c r="K353" t="s">
+        <v>1731</v>
       </c>
       <c r="L353">
         <v>0</v>
@@ -33873,6 +35238,9 @@
       <c r="C354" t="s">
         <v>843</v>
       </c>
+      <c r="D354">
+        <v>33</v>
+      </c>
       <c r="E354">
         <v>9000</v>
       </c>
@@ -33887,6 +35255,12 @@
       </c>
       <c r="I354" t="s">
         <v>1594</v>
+      </c>
+      <c r="J354" t="s">
+        <v>1729</v>
+      </c>
+      <c r="K354" t="s">
+        <v>1731</v>
       </c>
       <c r="L354">
         <v>1</v>
@@ -33947,9 +35321,15 @@
       <c r="C355" t="s">
         <v>842</v>
       </c>
+      <c r="D355">
+        <v>33</v>
+      </c>
       <c r="E355">
         <v>4800</v>
       </c>
+      <c r="F355">
+        <v>0</v>
+      </c>
       <c r="G355" s="1">
         <v>44201</v>
       </c>
@@ -33961,6 +35341,9 @@
       </c>
       <c r="J355" t="s">
         <v>1729</v>
+      </c>
+      <c r="K355" t="s">
+        <v>1731</v>
       </c>
       <c r="L355">
         <v>0</v>
@@ -34021,6 +35404,9 @@
       <c r="D356">
         <v>39</v>
       </c>
+      <c r="E356">
+        <v>6500</v>
+      </c>
       <c r="F356">
         <v>500</v>
       </c>
@@ -34095,6 +35481,9 @@
       <c r="E357">
         <v>8500</v>
       </c>
+      <c r="F357">
+        <v>0</v>
+      </c>
       <c r="G357" s="1">
         <v>45058</v>
       </c>
@@ -34181,6 +35570,9 @@
       <c r="E358">
         <v>6200</v>
       </c>
+      <c r="F358">
+        <v>0</v>
+      </c>
       <c r="G358" s="1">
         <v>44003</v>
       </c>
@@ -34189,6 +35581,12 @@
       </c>
       <c r="I358" t="s">
         <v>1597</v>
+      </c>
+      <c r="J358" t="s">
+        <v>1729</v>
+      </c>
+      <c r="K358" t="s">
+        <v>1731</v>
       </c>
       <c r="L358">
         <v>0</v>
@@ -34261,11 +35659,17 @@
       <c r="E359">
         <v>5750</v>
       </c>
+      <c r="F359">
+        <v>0</v>
+      </c>
       <c r="H359" t="s">
         <v>1167</v>
       </c>
       <c r="I359" t="s">
         <v>1598</v>
+      </c>
+      <c r="J359" t="s">
+        <v>1729</v>
       </c>
       <c r="K359" t="s">
         <v>1731</v>
@@ -34335,6 +35739,15 @@
       <c r="C360" t="s">
         <v>845</v>
       </c>
+      <c r="D360">
+        <v>33</v>
+      </c>
+      <c r="E360">
+        <v>6500</v>
+      </c>
+      <c r="F360">
+        <v>0</v>
+      </c>
       <c r="G360" s="1">
         <v>44842</v>
       </c>
@@ -34346,6 +35759,9 @@
       </c>
       <c r="J360" t="s">
         <v>1728</v>
+      </c>
+      <c r="K360" t="s">
+        <v>1731</v>
       </c>
       <c r="L360">
         <v>1</v>
@@ -34403,6 +35819,9 @@
       <c r="E361">
         <v>7000</v>
       </c>
+      <c r="F361">
+        <v>0</v>
+      </c>
       <c r="G361" s="1">
         <v>45388</v>
       </c>
@@ -34414,6 +35833,9 @@
       </c>
       <c r="J361" t="s">
         <v>1729</v>
+      </c>
+      <c r="K361" t="s">
+        <v>1731</v>
       </c>
       <c r="L361">
         <v>0</v>
@@ -34483,6 +35905,9 @@
       <c r="D362">
         <v>23</v>
       </c>
+      <c r="E362">
+        <v>6500</v>
+      </c>
       <c r="F362">
         <v>500</v>
       </c>
@@ -34494,6 +35919,9 @@
       </c>
       <c r="J362" t="s">
         <v>1728</v>
+      </c>
+      <c r="K362" t="s">
+        <v>1731</v>
       </c>
       <c r="L362">
         <v>0</v>
@@ -34551,8 +35979,14 @@
       <c r="C363" t="s">
         <v>841</v>
       </c>
+      <c r="D363">
+        <v>33</v>
+      </c>
       <c r="E363">
         <v>6000</v>
+      </c>
+      <c r="F363">
+        <v>0</v>
       </c>
       <c r="G363" s="1">
         <v>45446</v>
@@ -34720,6 +36154,9 @@
       <c r="E365">
         <v>9250</v>
       </c>
+      <c r="F365">
+        <v>0</v>
+      </c>
       <c r="G365" s="1">
         <v>45135</v>
       </c>
@@ -34731,6 +36168,9 @@
       </c>
       <c r="J365" t="s">
         <v>1728</v>
+      </c>
+      <c r="K365" t="s">
+        <v>1731</v>
       </c>
       <c r="L365">
         <v>0</v>
@@ -34797,6 +36237,9 @@
       <c r="D366">
         <v>-10</v>
       </c>
+      <c r="E366">
+        <v>6500</v>
+      </c>
       <c r="F366">
         <v>500</v>
       </c>
@@ -34886,6 +36329,9 @@
       <c r="J367" t="s">
         <v>1728</v>
       </c>
+      <c r="K367" t="s">
+        <v>1731</v>
+      </c>
       <c r="L367">
         <v>0</v>
       </c>
@@ -34972,6 +36418,9 @@
       <c r="J368" t="s">
         <v>1728</v>
       </c>
+      <c r="K368" t="s">
+        <v>1731</v>
+      </c>
       <c r="L368">
         <v>0</v>
       </c>
@@ -35034,6 +36483,15 @@
       <c r="C369" t="s">
         <v>842</v>
       </c>
+      <c r="D369">
+        <v>33</v>
+      </c>
+      <c r="E369">
+        <v>6500</v>
+      </c>
+      <c r="F369">
+        <v>0</v>
+      </c>
       <c r="G369" s="1">
         <v>43943</v>
       </c>
@@ -35102,11 +36560,17 @@
       <c r="E370">
         <v>5200</v>
       </c>
+      <c r="F370">
+        <v>0</v>
+      </c>
       <c r="G370" s="1">
         <v>45328</v>
       </c>
       <c r="H370" t="s">
         <v>1177</v>
+      </c>
+      <c r="J370" t="s">
+        <v>1729</v>
       </c>
       <c r="K370" t="s">
         <v>1732</v>
@@ -35182,6 +36646,9 @@
       <c r="E371">
         <v>8000</v>
       </c>
+      <c r="F371">
+        <v>0</v>
+      </c>
       <c r="G371" s="1">
         <v>43479</v>
       </c>
@@ -35190,6 +36657,9 @@
       </c>
       <c r="I371" t="s">
         <v>1609</v>
+      </c>
+      <c r="J371" t="s">
+        <v>1729</v>
       </c>
       <c r="K371" t="s">
         <v>1731</v>
@@ -35277,6 +36747,9 @@
       <c r="I372" t="s">
         <v>1610</v>
       </c>
+      <c r="J372" t="s">
+        <v>1729</v>
+      </c>
       <c r="K372" t="s">
         <v>1731</v>
       </c>
@@ -35345,6 +36818,12 @@
       <c r="C373" t="s">
         <v>843</v>
       </c>
+      <c r="D373">
+        <v>33</v>
+      </c>
+      <c r="E373">
+        <v>6500</v>
+      </c>
       <c r="F373">
         <v>-200</v>
       </c>
@@ -35425,6 +36904,12 @@
       <c r="H374" t="s">
         <v>1181</v>
       </c>
+      <c r="J374" t="s">
+        <v>1729</v>
+      </c>
+      <c r="K374" t="s">
+        <v>1731</v>
+      </c>
       <c r="L374">
         <v>0</v>
       </c>
@@ -35490,6 +36975,9 @@
       <c r="C375" t="s">
         <v>844</v>
       </c>
+      <c r="D375">
+        <v>33</v>
+      </c>
       <c r="E375">
         <v>7200</v>
       </c>
@@ -35573,6 +37061,9 @@
       <c r="D376">
         <v>38</v>
       </c>
+      <c r="E376">
+        <v>6500</v>
+      </c>
       <c r="F376">
         <v>500</v>
       </c>
@@ -35584,6 +37075,9 @@
       </c>
       <c r="I376" t="s">
         <v>1613</v>
+      </c>
+      <c r="J376" t="s">
+        <v>1729</v>
       </c>
       <c r="K376" t="s">
         <v>1731</v>
@@ -35736,6 +37230,9 @@
       <c r="E378">
         <v>4800</v>
       </c>
+      <c r="F378">
+        <v>0</v>
+      </c>
       <c r="G378" s="1">
         <v>44100</v>
       </c>
@@ -35747,6 +37244,9 @@
       </c>
       <c r="J378" t="s">
         <v>1728</v>
+      </c>
+      <c r="K378" t="s">
+        <v>1731</v>
       </c>
       <c r="L378">
         <v>0</v>
@@ -35899,6 +37399,15 @@
       <c r="C380" t="s">
         <v>840</v>
       </c>
+      <c r="D380">
+        <v>33</v>
+      </c>
+      <c r="E380">
+        <v>6500</v>
+      </c>
+      <c r="F380">
+        <v>0</v>
+      </c>
       <c r="G380" s="1">
         <v>43843</v>
       </c>
@@ -35970,6 +37479,9 @@
       <c r="E381">
         <v>6200</v>
       </c>
+      <c r="F381">
+        <v>0</v>
+      </c>
       <c r="G381" s="1">
         <v>44721</v>
       </c>
@@ -35978,6 +37490,9 @@
       </c>
       <c r="I381" t="s">
         <v>1618</v>
+      </c>
+      <c r="J381" t="s">
+        <v>1729</v>
       </c>
       <c r="K381" t="s">
         <v>1731</v>
@@ -36047,6 +37562,9 @@
       <c r="C382" t="s">
         <v>843</v>
       </c>
+      <c r="D382">
+        <v>33</v>
+      </c>
       <c r="E382">
         <v>4750</v>
       </c>
@@ -36130,6 +37648,9 @@
       <c r="D383">
         <v>30</v>
       </c>
+      <c r="E383">
+        <v>6500</v>
+      </c>
       <c r="F383">
         <v>250</v>
       </c>
@@ -36287,6 +37808,9 @@
       <c r="C385" t="s">
         <v>841</v>
       </c>
+      <c r="D385">
+        <v>33</v>
+      </c>
       <c r="E385">
         <v>5500</v>
       </c>
@@ -36370,6 +37894,9 @@
       <c r="E386">
         <v>7000</v>
       </c>
+      <c r="F386">
+        <v>0</v>
+      </c>
       <c r="G386" s="1">
         <v>43918</v>
       </c>
@@ -36378,6 +37905,9 @@
       </c>
       <c r="I386" t="s">
         <v>1622</v>
+      </c>
+      <c r="J386" t="s">
+        <v>1729</v>
       </c>
       <c r="K386" t="s">
         <v>1731</v>
@@ -36450,6 +37980,12 @@
       <c r="D387">
         <v>19</v>
       </c>
+      <c r="E387">
+        <v>6500</v>
+      </c>
+      <c r="F387">
+        <v>0</v>
+      </c>
       <c r="G387" s="1">
         <v>43906</v>
       </c>
@@ -36518,8 +38054,14 @@
       <c r="C388" t="s">
         <v>841</v>
       </c>
+      <c r="D388">
+        <v>33</v>
+      </c>
       <c r="E388">
         <v>6500</v>
+      </c>
+      <c r="F388">
+        <v>0</v>
       </c>
       <c r="G388" s="1">
         <v>45661</v>
@@ -36684,6 +38226,12 @@
       <c r="D390">
         <v>35</v>
       </c>
+      <c r="E390">
+        <v>6500</v>
+      </c>
+      <c r="F390">
+        <v>0</v>
+      </c>
       <c r="G390" s="1">
         <v>44055</v>
       </c>
@@ -36692,6 +38240,9 @@
       </c>
       <c r="I390" t="s">
         <v>1626</v>
+      </c>
+      <c r="J390" t="s">
+        <v>1729</v>
       </c>
       <c r="K390" t="s">
         <v>1732</v>
@@ -36767,6 +38318,9 @@
       <c r="H391" t="s">
         <v>1196</v>
       </c>
+      <c r="J391" t="s">
+        <v>1729</v>
+      </c>
       <c r="K391" t="s">
         <v>1732</v>
       </c>
@@ -36927,6 +38481,9 @@
       <c r="E393">
         <v>-500</v>
       </c>
+      <c r="F393">
+        <v>0</v>
+      </c>
       <c r="G393" s="1">
         <v>44176</v>
       </c>
@@ -37007,6 +38564,15 @@
       <c r="C394" t="s">
         <v>842</v>
       </c>
+      <c r="D394">
+        <v>33</v>
+      </c>
+      <c r="E394">
+        <v>6500</v>
+      </c>
+      <c r="F394">
+        <v>0</v>
+      </c>
       <c r="G394" s="1">
         <v>44404</v>
       </c>
@@ -37072,6 +38638,9 @@
       <c r="C395" t="s">
         <v>843</v>
       </c>
+      <c r="D395">
+        <v>33</v>
+      </c>
       <c r="E395">
         <v>7750</v>
       </c>
@@ -37173,6 +38742,9 @@
       <c r="J396" t="s">
         <v>1728</v>
       </c>
+      <c r="K396" t="s">
+        <v>1731</v>
+      </c>
       <c r="L396">
         <v>0</v>
       </c>
@@ -37241,6 +38813,9 @@
       <c r="D397">
         <v>41</v>
       </c>
+      <c r="E397">
+        <v>6500</v>
+      </c>
       <c r="F397">
         <v>250</v>
       </c>
@@ -37255,6 +38830,9 @@
       </c>
       <c r="J397" t="s">
         <v>1728</v>
+      </c>
+      <c r="K397" t="s">
+        <v>1731</v>
       </c>
       <c r="L397">
         <v>0</v>
@@ -37318,6 +38896,9 @@
       <c r="E398">
         <v>5000</v>
       </c>
+      <c r="F398">
+        <v>0</v>
+      </c>
       <c r="G398" s="1">
         <v>43523</v>
       </c>
@@ -37410,6 +38991,9 @@
       <c r="I399" t="s">
         <v>1633</v>
       </c>
+      <c r="J399" t="s">
+        <v>1729</v>
+      </c>
       <c r="K399" t="s">
         <v>1732</v>
       </c>
@@ -37475,6 +39059,9 @@
       <c r="C400" t="s">
         <v>845</v>
       </c>
+      <c r="D400">
+        <v>33</v>
+      </c>
       <c r="E400">
         <v>8500</v>
       </c>
@@ -37558,6 +39145,12 @@
       <c r="D401">
         <v>27</v>
       </c>
+      <c r="E401">
+        <v>6500</v>
+      </c>
+      <c r="F401">
+        <v>0</v>
+      </c>
       <c r="G401" s="1">
         <v>44454</v>
       </c>
@@ -37644,6 +39237,9 @@
       <c r="I402" t="s">
         <v>1331</v>
       </c>
+      <c r="J402" t="s">
+        <v>1729</v>
+      </c>
       <c r="K402" t="s">
         <v>1731</v>
       </c>
@@ -37712,9 +39308,15 @@
       <c r="C403" t="s">
         <v>841</v>
       </c>
+      <c r="D403">
+        <v>33</v>
+      </c>
       <c r="E403">
         <v>6250</v>
       </c>
+      <c r="F403">
+        <v>0</v>
+      </c>
       <c r="G403" s="1">
         <v>45094</v>
       </c>
@@ -37726,6 +39328,9 @@
       </c>
       <c r="J403" t="s">
         <v>1729</v>
+      </c>
+      <c r="K403" t="s">
+        <v>1731</v>
       </c>
       <c r="L403">
         <v>1</v>
@@ -37789,6 +39394,9 @@
       <c r="D404">
         <v>30</v>
       </c>
+      <c r="E404">
+        <v>6500</v>
+      </c>
       <c r="F404">
         <v>1000</v>
       </c>
@@ -37800,6 +39408,9 @@
       </c>
       <c r="I404" t="s">
         <v>1637</v>
+      </c>
+      <c r="J404" t="s">
+        <v>1729</v>
       </c>
       <c r="K404" t="s">
         <v>1731</v>
@@ -38124,6 +39735,15 @@
       <c r="C408" t="s">
         <v>843</v>
       </c>
+      <c r="D408">
+        <v>33</v>
+      </c>
+      <c r="E408">
+        <v>6500</v>
+      </c>
+      <c r="F408">
+        <v>0</v>
+      </c>
       <c r="G408" s="1">
         <v>44479</v>
       </c>
@@ -38189,6 +39809,9 @@
       <c r="C409" t="s">
         <v>842</v>
       </c>
+      <c r="D409">
+        <v>33</v>
+      </c>
       <c r="E409">
         <v>5750</v>
       </c>
@@ -38206,6 +39829,9 @@
       </c>
       <c r="J409" t="s">
         <v>1729</v>
+      </c>
+      <c r="K409" t="s">
+        <v>1731</v>
       </c>
       <c r="L409">
         <v>0</v>
@@ -38287,6 +39913,9 @@
       <c r="J410" t="s">
         <v>1730</v>
       </c>
+      <c r="K410" t="s">
+        <v>1731</v>
+      </c>
       <c r="L410">
         <v>0</v>
       </c>
@@ -38352,6 +39981,9 @@
       <c r="D411">
         <v>45</v>
       </c>
+      <c r="E411">
+        <v>6500</v>
+      </c>
       <c r="F411">
         <v>500</v>
       </c>
@@ -38512,6 +40144,9 @@
       <c r="C413" t="s">
         <v>845</v>
       </c>
+      <c r="D413">
+        <v>33</v>
+      </c>
       <c r="E413">
         <v>5200</v>
       </c>
@@ -38595,6 +40230,9 @@
       <c r="E414">
         <v>-2000</v>
       </c>
+      <c r="F414">
+        <v>0</v>
+      </c>
       <c r="G414" s="1">
         <v>45575</v>
       </c>
@@ -38603,6 +40241,12 @@
       </c>
       <c r="I414" t="s">
         <v>1647</v>
+      </c>
+      <c r="J414" t="s">
+        <v>1729</v>
+      </c>
+      <c r="K414" t="s">
+        <v>1731</v>
       </c>
       <c r="L414">
         <v>0</v>
@@ -38666,6 +40310,12 @@
       <c r="C415" t="s">
         <v>843</v>
       </c>
+      <c r="D415">
+        <v>33</v>
+      </c>
+      <c r="E415">
+        <v>6500</v>
+      </c>
       <c r="F415">
         <v>0</v>
       </c>
@@ -38677,6 +40327,9 @@
       </c>
       <c r="I415" t="s">
         <v>1648</v>
+      </c>
+      <c r="J415" t="s">
+        <v>1729</v>
       </c>
       <c r="K415" t="s">
         <v>1731</v>
@@ -38752,6 +40405,9 @@
       <c r="J416" t="s">
         <v>1729</v>
       </c>
+      <c r="K416" t="s">
+        <v>1731</v>
+      </c>
       <c r="L416">
         <v>0</v>
       </c>
@@ -38909,6 +40565,9 @@
       <c r="D418">
         <v>42</v>
       </c>
+      <c r="E418">
+        <v>6500</v>
+      </c>
       <c r="F418">
         <v>1000</v>
       </c>
@@ -39158,8 +40817,14 @@
       <c r="C421" t="s">
         <v>840</v>
       </c>
+      <c r="D421">
+        <v>33</v>
+      </c>
       <c r="E421">
         <v>5500</v>
+      </c>
+      <c r="F421">
+        <v>0</v>
       </c>
       <c r="G421" s="1">
         <v>44799</v>
@@ -39229,6 +40894,12 @@
       <c r="C422" t="s">
         <v>843</v>
       </c>
+      <c r="D422">
+        <v>33</v>
+      </c>
+      <c r="E422">
+        <v>6500</v>
+      </c>
       <c r="F422">
         <v>300</v>
       </c>
@@ -39475,6 +41146,12 @@
       <c r="D425">
         <v>20</v>
       </c>
+      <c r="E425">
+        <v>6500</v>
+      </c>
+      <c r="F425">
+        <v>0</v>
+      </c>
       <c r="H425" t="s">
         <v>1227</v>
       </c>
@@ -39549,6 +41226,9 @@
       <c r="E426">
         <v>5250</v>
       </c>
+      <c r="F426">
+        <v>0</v>
+      </c>
       <c r="G426" s="1">
         <v>45202</v>
       </c>
@@ -39629,6 +41309,9 @@
       <c r="C427" t="s">
         <v>841</v>
       </c>
+      <c r="D427">
+        <v>33</v>
+      </c>
       <c r="E427">
         <v>7200</v>
       </c>
@@ -39801,6 +41484,9 @@
       <c r="D429">
         <v>47</v>
       </c>
+      <c r="E429">
+        <v>6500</v>
+      </c>
       <c r="F429">
         <v>300</v>
       </c>
@@ -39875,6 +41561,9 @@
       <c r="C430" t="s">
         <v>843</v>
       </c>
+      <c r="D430">
+        <v>33</v>
+      </c>
       <c r="E430">
         <v>6500</v>
       </c>
@@ -39949,6 +41638,9 @@
       <c r="D431">
         <v>35</v>
       </c>
+      <c r="E431">
+        <v>6500</v>
+      </c>
       <c r="F431">
         <v>250</v>
       </c>
@@ -39960,6 +41652,9 @@
       </c>
       <c r="I431" t="s">
         <v>1663</v>
+      </c>
+      <c r="J431" t="s">
+        <v>1729</v>
       </c>
       <c r="K431" t="s">
         <v>1731</v>
@@ -40026,6 +41721,9 @@
       <c r="E432">
         <v>6800</v>
       </c>
+      <c r="F432">
+        <v>0</v>
+      </c>
       <c r="G432" s="1">
         <v>43835</v>
       </c>
@@ -40118,6 +41816,9 @@
       <c r="J433" t="s">
         <v>1729</v>
       </c>
+      <c r="K433" t="s">
+        <v>1731</v>
+      </c>
       <c r="L433">
         <v>0</v>
       </c>
@@ -40272,6 +41973,9 @@
       <c r="C435" t="s">
         <v>842</v>
       </c>
+      <c r="D435">
+        <v>33</v>
+      </c>
       <c r="E435">
         <v>-1500</v>
       </c>
@@ -40352,6 +42056,15 @@
       <c r="C436" t="s">
         <v>843</v>
       </c>
+      <c r="D436">
+        <v>33</v>
+      </c>
+      <c r="E436">
+        <v>6500</v>
+      </c>
+      <c r="F436">
+        <v>0</v>
+      </c>
       <c r="G436" s="1">
         <v>44000</v>
       </c>
@@ -40414,6 +42127,9 @@
       <c r="E437">
         <v>5500</v>
       </c>
+      <c r="F437">
+        <v>0</v>
+      </c>
       <c r="G437" s="1">
         <v>43895</v>
       </c>
@@ -40500,6 +42216,9 @@
       <c r="E438">
         <v>7000</v>
       </c>
+      <c r="F438">
+        <v>0</v>
+      </c>
       <c r="G438" s="1">
         <v>43520</v>
       </c>
@@ -40583,6 +42302,9 @@
       <c r="D439">
         <v>28</v>
       </c>
+      <c r="E439">
+        <v>6500</v>
+      </c>
       <c r="F439">
         <v>1000</v>
       </c>
@@ -40657,6 +42379,9 @@
       <c r="C440" t="s">
         <v>843</v>
       </c>
+      <c r="D440">
+        <v>33</v>
+      </c>
       <c r="E440">
         <v>9250</v>
       </c>
@@ -40755,6 +42480,9 @@
       <c r="I441" t="s">
         <v>1672</v>
       </c>
+      <c r="J441" t="s">
+        <v>1729</v>
+      </c>
       <c r="K441" t="s">
         <v>1731</v>
       </c>
@@ -40823,8 +42551,14 @@
       <c r="C442" t="s">
         <v>842</v>
       </c>
+      <c r="D442">
+        <v>33</v>
+      </c>
       <c r="E442">
         <v>6500</v>
+      </c>
+      <c r="F442">
+        <v>0</v>
       </c>
       <c r="G442" s="1">
         <v>45315</v>
@@ -40903,6 +42637,12 @@
       <c r="D443">
         <v>41</v>
       </c>
+      <c r="E443">
+        <v>6500</v>
+      </c>
+      <c r="F443">
+        <v>0</v>
+      </c>
       <c r="G443" s="1">
         <v>44320</v>
       </c>
@@ -41146,6 +42886,12 @@
       <c r="D446">
         <v>-6</v>
       </c>
+      <c r="E446">
+        <v>6500</v>
+      </c>
+      <c r="F446">
+        <v>0</v>
+      </c>
       <c r="G446" s="1">
         <v>45072</v>
       </c>
@@ -41157,6 +42903,9 @@
       </c>
       <c r="J446" t="s">
         <v>1729</v>
+      </c>
+      <c r="K446" t="s">
+        <v>1731</v>
       </c>
       <c r="L446">
         <v>0</v>
@@ -41217,6 +42966,9 @@
       <c r="E447">
         <v>7000</v>
       </c>
+      <c r="F447">
+        <v>0</v>
+      </c>
       <c r="G447" s="1">
         <v>44139</v>
       </c>
@@ -41297,9 +43049,15 @@
       <c r="C448" t="s">
         <v>840</v>
       </c>
+      <c r="D448">
+        <v>33</v>
+      </c>
       <c r="E448">
         <v>6200</v>
       </c>
+      <c r="F448">
+        <v>0</v>
+      </c>
       <c r="G448" s="1">
         <v>44697</v>
       </c>
@@ -41311,6 +43069,9 @@
       </c>
       <c r="J448" t="s">
         <v>1729</v>
+      </c>
+      <c r="K448" t="s">
+        <v>1731</v>
       </c>
       <c r="L448">
         <v>1</v>
@@ -41368,6 +43129,9 @@
       <c r="C449" t="s">
         <v>844</v>
       </c>
+      <c r="D449">
+        <v>33</v>
+      </c>
       <c r="E449">
         <v>5750</v>
       </c>
@@ -41445,6 +43209,9 @@
       <c r="D450">
         <v>29</v>
       </c>
+      <c r="E450">
+        <v>6500</v>
+      </c>
       <c r="F450">
         <v>1000</v>
       </c>
@@ -41453,6 +43220,9 @@
       </c>
       <c r="I450" t="s">
         <v>1681</v>
+      </c>
+      <c r="J450" t="s">
+        <v>1729</v>
       </c>
       <c r="K450" t="s">
         <v>1731</v>
@@ -41516,6 +43286,9 @@
       <c r="E451">
         <v>8500</v>
       </c>
+      <c r="F451">
+        <v>0</v>
+      </c>
       <c r="G451" s="1">
         <v>45272</v>
       </c>
@@ -41602,6 +43375,9 @@
       <c r="E452">
         <v>4500</v>
       </c>
+      <c r="F452">
+        <v>0</v>
+      </c>
       <c r="G452" s="1">
         <v>45487</v>
       </c>
@@ -41685,6 +43461,9 @@
       <c r="D453">
         <v>45</v>
       </c>
+      <c r="E453">
+        <v>6500</v>
+      </c>
       <c r="F453">
         <v>1250</v>
       </c>
@@ -41759,6 +43538,9 @@
       <c r="C454" t="s">
         <v>840</v>
       </c>
+      <c r="D454">
+        <v>33</v>
+      </c>
       <c r="E454">
         <v>6250</v>
       </c>
@@ -41842,6 +43624,9 @@
       <c r="E455">
         <v>9000</v>
       </c>
+      <c r="F455">
+        <v>0</v>
+      </c>
       <c r="G455" s="1">
         <v>44310</v>
       </c>
@@ -41850,6 +43635,9 @@
       </c>
       <c r="J455" t="s">
         <v>1729</v>
+      </c>
+      <c r="K455" t="s">
+        <v>1731</v>
       </c>
       <c r="L455">
         <v>0</v>
@@ -41937,6 +43725,9 @@
       <c r="J456" t="s">
         <v>1730</v>
       </c>
+      <c r="K456" t="s">
+        <v>1731</v>
+      </c>
       <c r="L456">
         <v>0</v>
       </c>
@@ -42002,6 +43793,12 @@
       <c r="C457" t="s">
         <v>841</v>
       </c>
+      <c r="D457">
+        <v>33</v>
+      </c>
+      <c r="E457">
+        <v>6500</v>
+      </c>
       <c r="F457">
         <v>300</v>
       </c>
@@ -42073,6 +43870,9 @@
       <c r="E458">
         <v>5000</v>
       </c>
+      <c r="F458">
+        <v>0</v>
+      </c>
       <c r="G458" s="1">
         <v>45068</v>
       </c>
@@ -42081,6 +43881,9 @@
       </c>
       <c r="I458" t="s">
         <v>1688</v>
+      </c>
+      <c r="J458" t="s">
+        <v>1729</v>
       </c>
       <c r="K458" t="s">
         <v>1731</v>
@@ -42239,6 +44042,9 @@
       <c r="D460">
         <v>42</v>
       </c>
+      <c r="E460">
+        <v>6500</v>
+      </c>
       <c r="F460">
         <v>0</v>
       </c>
@@ -42250,6 +44056,12 @@
       </c>
       <c r="I460" t="s">
         <v>1690</v>
+      </c>
+      <c r="J460" t="s">
+        <v>1729</v>
+      </c>
+      <c r="K460" t="s">
+        <v>1731</v>
       </c>
       <c r="L460">
         <v>0</v>
@@ -42313,6 +44125,9 @@
       <c r="E461">
         <v>7500</v>
       </c>
+      <c r="F461">
+        <v>0</v>
+      </c>
       <c r="G461" s="1">
         <v>45494</v>
       </c>
@@ -42393,6 +44208,9 @@
       <c r="C462" t="s">
         <v>843</v>
       </c>
+      <c r="D462">
+        <v>33</v>
+      </c>
       <c r="E462">
         <v>5500</v>
       </c>
@@ -42470,6 +44288,9 @@
       <c r="C463" t="s">
         <v>844</v>
       </c>
+      <c r="D463">
+        <v>33</v>
+      </c>
       <c r="E463">
         <v>8000</v>
       </c>
@@ -42484,6 +44305,12 @@
       </c>
       <c r="I463" t="s">
         <v>1693</v>
+      </c>
+      <c r="J463" t="s">
+        <v>1729</v>
+      </c>
+      <c r="K463" t="s">
+        <v>1731</v>
       </c>
       <c r="L463">
         <v>0</v>
@@ -42547,6 +44374,9 @@
       <c r="D464">
         <v>39</v>
       </c>
+      <c r="E464">
+        <v>6500</v>
+      </c>
       <c r="F464">
         <v>750</v>
       </c>
@@ -42704,6 +44534,9 @@
       <c r="D466">
         <v>30</v>
       </c>
+      <c r="E466">
+        <v>6500</v>
+      </c>
       <c r="F466">
         <v>500</v>
       </c>
@@ -42715,6 +44548,9 @@
       </c>
       <c r="I466" t="s">
         <v>1696</v>
+      </c>
+      <c r="J466" t="s">
+        <v>1729</v>
       </c>
       <c r="K466" t="s">
         <v>1731</v>
@@ -42775,6 +44611,9 @@
       <c r="C467" t="s">
         <v>841</v>
       </c>
+      <c r="D467">
+        <v>33</v>
+      </c>
       <c r="E467">
         <v>4800</v>
       </c>
@@ -42938,6 +44777,9 @@
       <c r="C469" t="s">
         <v>841</v>
       </c>
+      <c r="D469">
+        <v>33</v>
+      </c>
       <c r="E469">
         <v>6200</v>
       </c>
@@ -42952,6 +44794,9 @@
       </c>
       <c r="I469" t="s">
         <v>1698</v>
+      </c>
+      <c r="J469" t="s">
+        <v>1729</v>
       </c>
       <c r="K469" t="s">
         <v>1732</v>
@@ -43018,6 +44863,9 @@
       <c r="D470">
         <v>46</v>
       </c>
+      <c r="E470">
+        <v>6500</v>
+      </c>
       <c r="F470">
         <v>750</v>
       </c>
@@ -43098,6 +44946,9 @@
       <c r="E471">
         <v>6500</v>
       </c>
+      <c r="F471">
+        <v>0</v>
+      </c>
       <c r="G471" s="1">
         <v>44433</v>
       </c>
@@ -43270,6 +45121,9 @@
       <c r="D473">
         <v>-3</v>
       </c>
+      <c r="E473">
+        <v>6500</v>
+      </c>
       <c r="F473">
         <v>750</v>
       </c>
@@ -43353,6 +45207,9 @@
       <c r="I474" t="s">
         <v>1703</v>
       </c>
+      <c r="J474" t="s">
+        <v>1729</v>
+      </c>
       <c r="K474" t="s">
         <v>1731</v>
       </c>
@@ -43421,6 +45278,9 @@
       <c r="C475" t="s">
         <v>841</v>
       </c>
+      <c r="D475">
+        <v>33</v>
+      </c>
       <c r="E475">
         <v>5500</v>
       </c>
@@ -43435,6 +45295,9 @@
       </c>
       <c r="I475" t="s">
         <v>1704</v>
+      </c>
+      <c r="J475" t="s">
+        <v>1729</v>
       </c>
       <c r="K475" t="s">
         <v>1732</v>
@@ -43498,8 +45361,14 @@
       <c r="C476" t="s">
         <v>841</v>
       </c>
+      <c r="D476">
+        <v>33</v>
+      </c>
       <c r="E476">
         <v>-1000</v>
+      </c>
+      <c r="F476">
+        <v>0</v>
       </c>
       <c r="G476" s="1">
         <v>43709</v>
@@ -43572,6 +45441,12 @@
       <c r="D477">
         <v>25</v>
       </c>
+      <c r="E477">
+        <v>6500</v>
+      </c>
+      <c r="F477">
+        <v>0</v>
+      </c>
       <c r="G477" s="1">
         <v>44979</v>
       </c>
@@ -43750,6 +45625,12 @@
       <c r="I479" t="s">
         <v>1708</v>
       </c>
+      <c r="J479" t="s">
+        <v>1729</v>
+      </c>
+      <c r="K479" t="s">
+        <v>1731</v>
+      </c>
       <c r="L479">
         <v>0</v>
       </c>
@@ -43818,6 +45699,9 @@
       <c r="D480">
         <v>44</v>
       </c>
+      <c r="E480">
+        <v>6500</v>
+      </c>
       <c r="F480">
         <v>750</v>
       </c>
@@ -43832,6 +45716,9 @@
       </c>
       <c r="J480" t="s">
         <v>1729</v>
+      </c>
+      <c r="K480" t="s">
+        <v>1731</v>
       </c>
       <c r="L480">
         <v>0</v>
@@ -43889,6 +45776,9 @@
       <c r="C481" t="s">
         <v>842</v>
       </c>
+      <c r="D481">
+        <v>33</v>
+      </c>
       <c r="E481">
         <v>5250</v>
       </c>
@@ -43906,6 +45796,9 @@
       </c>
       <c r="J481" t="s">
         <v>1729</v>
+      </c>
+      <c r="K481" t="s">
+        <v>1731</v>
       </c>
       <c r="L481">
         <v>1</v>
@@ -43972,6 +45865,9 @@
       <c r="E482">
         <v>9000</v>
       </c>
+      <c r="F482">
+        <v>0</v>
+      </c>
       <c r="G482" s="1">
         <v>45217</v>
       </c>
@@ -43983,6 +45879,9 @@
       </c>
       <c r="J482" t="s">
         <v>1729</v>
+      </c>
+      <c r="K482" t="s">
+        <v>1731</v>
       </c>
       <c r="L482">
         <v>0</v>
@@ -44132,6 +46031,12 @@
       <c r="C484" t="s">
         <v>841</v>
       </c>
+      <c r="D484">
+        <v>33</v>
+      </c>
+      <c r="E484">
+        <v>6500</v>
+      </c>
       <c r="F484">
         <v>0</v>
       </c>
@@ -44143,6 +46048,12 @@
       </c>
       <c r="I484" t="s">
         <v>1713</v>
+      </c>
+      <c r="J484" t="s">
+        <v>1729</v>
+      </c>
+      <c r="K484" t="s">
+        <v>1731</v>
       </c>
       <c r="L484">
         <v>1</v>
@@ -44286,11 +46197,20 @@
       <c r="D486">
         <v>160</v>
       </c>
+      <c r="E486">
+        <v>6500</v>
+      </c>
+      <c r="F486">
+        <v>0</v>
+      </c>
       <c r="G486" s="1">
         <v>45282</v>
       </c>
       <c r="H486" t="s">
         <v>1276</v>
+      </c>
+      <c r="J486" t="s">
+        <v>1729</v>
       </c>
       <c r="K486" t="s">
         <v>1731</v>
@@ -44354,6 +46274,9 @@
       <c r="E487">
         <v>4500</v>
       </c>
+      <c r="F487">
+        <v>0</v>
+      </c>
       <c r="G487" s="1">
         <v>45623</v>
       </c>
@@ -44452,6 +46375,9 @@
       <c r="J488" t="s">
         <v>1728</v>
       </c>
+      <c r="K488" t="s">
+        <v>1731</v>
+      </c>
       <c r="L488">
         <v>0</v>
       </c>
@@ -44517,6 +46443,9 @@
       <c r="C489" t="s">
         <v>843</v>
       </c>
+      <c r="D489">
+        <v>33</v>
+      </c>
       <c r="E489">
         <v>5200</v>
       </c>
@@ -44597,6 +46526,12 @@
       <c r="C490" t="s">
         <v>842</v>
       </c>
+      <c r="D490">
+        <v>33</v>
+      </c>
+      <c r="E490">
+        <v>6500</v>
+      </c>
       <c r="F490">
         <v>500</v>
       </c>
@@ -44608,6 +46543,9 @@
       </c>
       <c r="I490" t="s">
         <v>1718</v>
+      </c>
+      <c r="J490" t="s">
+        <v>1729</v>
       </c>
       <c r="K490" t="s">
         <v>1732</v>
@@ -44769,6 +46707,9 @@
       <c r="I492" t="s">
         <v>1720</v>
       </c>
+      <c r="J492" t="s">
+        <v>1729</v>
+      </c>
       <c r="K492" t="s">
         <v>1731</v>
       </c>
@@ -44840,6 +46781,12 @@
       <c r="D493">
         <v>36</v>
       </c>
+      <c r="E493">
+        <v>6500</v>
+      </c>
+      <c r="F493">
+        <v>0</v>
+      </c>
       <c r="G493" s="1">
         <v>45300</v>
       </c>
@@ -44911,6 +46858,9 @@
       <c r="C494" t="s">
         <v>844</v>
       </c>
+      <c r="D494">
+        <v>33</v>
+      </c>
       <c r="E494">
         <v>5500</v>
       </c>
@@ -44925,6 +46875,9 @@
       </c>
       <c r="J494" t="s">
         <v>1728</v>
+      </c>
+      <c r="K494" t="s">
+        <v>1731</v>
       </c>
       <c r="L494">
         <v>1</v>
@@ -44988,6 +46941,9 @@
       <c r="E495">
         <v>9000</v>
       </c>
+      <c r="F495">
+        <v>0</v>
+      </c>
       <c r="G495" s="1">
         <v>44341</v>
       </c>
@@ -44996,6 +46952,9 @@
       </c>
       <c r="J495" t="s">
         <v>1729</v>
+      </c>
+      <c r="K495" t="s">
+        <v>1731</v>
       </c>
       <c r="L495">
         <v>0</v>
@@ -45059,6 +47018,9 @@
       <c r="C496" t="s">
         <v>843</v>
       </c>
+      <c r="D496">
+        <v>33</v>
+      </c>
       <c r="E496">
         <v>6250</v>
       </c>
@@ -45139,6 +47101,9 @@
       <c r="D497">
         <v>45</v>
       </c>
+      <c r="E497">
+        <v>6500</v>
+      </c>
       <c r="F497">
         <v>-50</v>
       </c>
@@ -45302,6 +47267,9 @@
       <c r="D499">
         <v>27</v>
       </c>
+      <c r="E499">
+        <v>6500</v>
+      </c>
       <c r="F499">
         <v>300</v>
       </c>
@@ -45381,6 +47349,9 @@
       </c>
       <c r="E500">
         <v>6200</v>
+      </c>
+      <c r="F500">
+        <v>0</v>
       </c>
       <c r="G500" s="1">
         <v>45215</v>

--- a/data/cleaned_data.xlsx
+++ b/data/cleaned_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5429" uniqueCount="1749">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5431" uniqueCount="1749">
   <si>
     <t>employee_id</t>
   </si>
@@ -5239,10 +5239,10 @@
     <t>Low</t>
   </si>
   <si>
+    <t>High</t>
+  </si>
+  <si>
     <t>Medium</t>
-  </si>
-  <si>
-    <t>High</t>
   </si>
   <si>
     <t>Young</t>
@@ -5788,7 +5788,7 @@
         <v>30</v>
       </c>
       <c r="E3">
-        <v>6000</v>
+        <v>16000</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -5839,7 +5839,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" t="b">
         <v>0</v>
@@ -5874,7 +5874,7 @@
         <v>35</v>
       </c>
       <c r="E4">
-        <v>7500.5</v>
+        <v>7501</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -5937,10 +5937,10 @@
         <v>0</v>
       </c>
       <c r="Z4" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA4" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB4" t="s">
         <v>1744</v>
@@ -6100,10 +6100,10 @@
         <v>0</v>
       </c>
       <c r="Z6" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA6" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB6" t="s">
         <v>1745</v>
@@ -6186,10 +6186,10 @@
         <v>0</v>
       </c>
       <c r="Z7" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA7" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC7" t="s">
         <v>1747</v>
@@ -6212,7 +6212,7 @@
         <v>7200</v>
       </c>
       <c r="F8">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="H8" t="s">
         <v>852</v>
@@ -6263,10 +6263,10 @@
         <v>0</v>
       </c>
       <c r="Z8" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA8" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB8" t="s">
         <v>1744</v>
@@ -6289,7 +6289,7 @@
         <v>33</v>
       </c>
       <c r="E9">
-        <v>6500</v>
+        <v>0</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -6313,7 +6313,7 @@
         <v>1</v>
       </c>
       <c r="M9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -6339,11 +6339,20 @@
       <c r="U9" t="b">
         <v>0</v>
       </c>
+      <c r="V9" t="b">
+        <v>1</v>
+      </c>
       <c r="X9" t="b">
         <v>1</v>
       </c>
       <c r="Y9" t="b">
         <v>1</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>1740</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>1740</v>
       </c>
       <c r="AC9" t="s">
         <v>1747</v>
@@ -6411,7 +6420,7 @@
         <v>1</v>
       </c>
       <c r="U10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" t="b">
         <v>0</v>
@@ -6426,10 +6435,10 @@
         <v>0</v>
       </c>
       <c r="Z10" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA10" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AC10" t="s">
         <v>1747</v>
@@ -6595,10 +6604,10 @@
         <v>0</v>
       </c>
       <c r="Z12" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA12" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB12" t="s">
         <v>1744</v>
@@ -6841,10 +6850,10 @@
         <v>0</v>
       </c>
       <c r="Z15" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA15" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB15" t="s">
         <v>1744</v>
@@ -6930,10 +6939,10 @@
         <v>0</v>
       </c>
       <c r="Z16" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA16" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB16" t="s">
         <v>1745</v>
@@ -7019,10 +7028,10 @@
         <v>0</v>
       </c>
       <c r="Z17" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA17" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB17" t="s">
         <v>1744</v>
@@ -7280,10 +7289,10 @@
         <v>0</v>
       </c>
       <c r="Z20" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA20" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB20" t="s">
         <v>1745</v>
@@ -7449,10 +7458,10 @@
         <v>0</v>
       </c>
       <c r="Z22" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA22" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB22" t="s">
         <v>1745</v>
@@ -7606,7 +7615,7 @@
         <v>1</v>
       </c>
       <c r="U24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" t="b">
         <v>0</v>
@@ -7618,10 +7627,10 @@
         <v>0</v>
       </c>
       <c r="Z24" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA24" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AC24" t="s">
         <v>1747</v>
@@ -7864,10 +7873,10 @@
         <v>0</v>
       </c>
       <c r="Z27" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA27" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB27" t="s">
         <v>1744</v>
@@ -7944,10 +7953,10 @@
         <v>0</v>
       </c>
       <c r="Z28" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA28" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB28" t="s">
         <v>1745</v>
@@ -8110,10 +8119,10 @@
         <v>0</v>
       </c>
       <c r="Z30" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA30" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB30" t="s">
         <v>1744</v>
@@ -8276,10 +8285,10 @@
         <v>0</v>
       </c>
       <c r="Z32" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA32" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC32" t="s">
         <v>1747</v>
@@ -8451,10 +8460,10 @@
         <v>0</v>
       </c>
       <c r="Z34" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA34" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB34" t="s">
         <v>1745</v>
@@ -8531,10 +8540,10 @@
         <v>0</v>
       </c>
       <c r="Z35" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA35" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB35" t="s">
         <v>1744</v>
@@ -8691,10 +8700,10 @@
         <v>0</v>
       </c>
       <c r="Z37" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA37" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB37" t="s">
         <v>1744</v>
@@ -8777,10 +8786,10 @@
         <v>0</v>
       </c>
       <c r="Z38" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA38" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB38" t="s">
         <v>1743</v>
@@ -8842,7 +8851,7 @@
         <v>1</v>
       </c>
       <c r="U39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V39" t="b">
         <v>0</v>
@@ -9112,10 +9121,10 @@
         <v>0</v>
       </c>
       <c r="Z42" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA42" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB42" t="s">
         <v>1745</v>
@@ -9195,10 +9204,10 @@
         <v>0</v>
       </c>
       <c r="Z43" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA43" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC43" t="s">
         <v>1747</v>
@@ -9355,7 +9364,7 @@
         <v>0</v>
       </c>
       <c r="U45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" t="b">
         <v>1</v>
@@ -9438,7 +9447,7 @@
         <v>1</v>
       </c>
       <c r="U46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V46" t="b">
         <v>0</v>
@@ -9453,10 +9462,10 @@
         <v>0</v>
       </c>
       <c r="Z46" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA46" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB46" t="s">
         <v>1744</v>
@@ -9622,10 +9631,10 @@
         <v>0</v>
       </c>
       <c r="Z48" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA48" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB48" t="s">
         <v>1744</v>
@@ -9711,10 +9720,10 @@
         <v>0</v>
       </c>
       <c r="Z49" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA49" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB49" t="s">
         <v>1743</v>
@@ -9948,7 +9957,7 @@
         <v>1</v>
       </c>
       <c r="U52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V52" t="b">
         <v>0</v>
@@ -9963,10 +9972,10 @@
         <v>0</v>
       </c>
       <c r="Z52" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA52" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB52" t="s">
         <v>1745</v>
@@ -10052,10 +10061,10 @@
         <v>0</v>
       </c>
       <c r="Z53" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA53" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB53" t="s">
         <v>1744</v>
@@ -10289,10 +10298,10 @@
         <v>0</v>
       </c>
       <c r="Z56" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA56" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB56" t="s">
         <v>1744</v>
@@ -10461,10 +10470,10 @@
         <v>0</v>
       </c>
       <c r="Z58" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA58" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB58" t="s">
         <v>1743</v>
@@ -10550,10 +10559,10 @@
         <v>0</v>
       </c>
       <c r="Z59" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA59" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC59" t="s">
         <v>1747</v>
@@ -10882,10 +10891,10 @@
         <v>0</v>
       </c>
       <c r="Z63" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA63" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB63" t="s">
         <v>1745</v>
@@ -10968,10 +10977,10 @@
         <v>0</v>
       </c>
       <c r="Z64" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA64" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB64" t="s">
         <v>1743</v>
@@ -11125,10 +11134,10 @@
         <v>0</v>
       </c>
       <c r="Z66" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA66" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB66" t="s">
         <v>1744</v>
@@ -11297,10 +11306,10 @@
         <v>0</v>
       </c>
       <c r="Z68" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA68" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB68" t="s">
         <v>1745</v>
@@ -11457,10 +11466,10 @@
         <v>0</v>
       </c>
       <c r="Z70" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA70" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB70" t="s">
         <v>1744</v>
@@ -11626,10 +11635,10 @@
         <v>0</v>
       </c>
       <c r="Z72" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA72" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB72" t="s">
         <v>1745</v>
@@ -11780,7 +11789,7 @@
         <v>1</v>
       </c>
       <c r="U74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V74" t="b">
         <v>0</v>
@@ -11875,10 +11884,10 @@
         <v>0</v>
       </c>
       <c r="Z75" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA75" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB75" t="s">
         <v>1744</v>
@@ -11964,10 +11973,10 @@
         <v>0</v>
       </c>
       <c r="Z76" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA76" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB76" t="s">
         <v>1745</v>
@@ -12050,10 +12059,10 @@
         <v>0</v>
       </c>
       <c r="Z77" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA77" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB77" t="s">
         <v>1744</v>
@@ -12213,10 +12222,10 @@
         <v>0</v>
       </c>
       <c r="Z79" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA79" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB79" t="s">
         <v>1745</v>
@@ -12459,10 +12468,10 @@
         <v>0</v>
       </c>
       <c r="Z82" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA82" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB82" t="s">
         <v>1745</v>
@@ -12720,10 +12729,10 @@
         <v>0</v>
       </c>
       <c r="Z85" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA85" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AC85" t="s">
         <v>1747</v>
@@ -12883,10 +12892,10 @@
         <v>0</v>
       </c>
       <c r="Z87" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA87" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB87" t="s">
         <v>1744</v>
@@ -12972,10 +12981,10 @@
         <v>0</v>
       </c>
       <c r="Z88" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA88" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC88" t="s">
         <v>1747</v>
@@ -13135,10 +13144,10 @@
         <v>0</v>
       </c>
       <c r="Z90" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA90" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB90" t="s">
         <v>1744</v>
@@ -13304,10 +13313,10 @@
         <v>0</v>
       </c>
       <c r="Z92" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA92" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC92" t="s">
         <v>1747</v>
@@ -13390,10 +13399,10 @@
         <v>0</v>
       </c>
       <c r="Z93" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA93" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB93" t="s">
         <v>1743</v>
@@ -13639,10 +13648,10 @@
         <v>0</v>
       </c>
       <c r="Z96" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA96" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB96" t="s">
         <v>1744</v>
@@ -13897,10 +13906,10 @@
         <v>0</v>
       </c>
       <c r="Z99" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA99" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB99" t="s">
         <v>1743</v>
@@ -14066,10 +14075,10 @@
         <v>0</v>
       </c>
       <c r="Z101" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA101" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB101" t="s">
         <v>1744</v>
@@ -14229,10 +14238,10 @@
         <v>0</v>
       </c>
       <c r="Z103" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA103" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC103" t="s">
         <v>1747</v>
@@ -14398,10 +14407,10 @@
         <v>0</v>
       </c>
       <c r="Z105" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA105" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB105" t="s">
         <v>1744</v>
@@ -14567,10 +14576,10 @@
         <v>0</v>
       </c>
       <c r="Z107" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA107" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB107" t="s">
         <v>1744</v>
@@ -14739,10 +14748,10 @@
         <v>0</v>
       </c>
       <c r="Z109" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA109" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC109" t="s">
         <v>1747</v>
@@ -14905,10 +14914,10 @@
         <v>0</v>
       </c>
       <c r="Z111" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA111" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB111" t="s">
         <v>1744</v>
@@ -15077,10 +15086,10 @@
         <v>0</v>
       </c>
       <c r="Z113" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA113" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB113" t="s">
         <v>1743</v>
@@ -15240,10 +15249,10 @@
         <v>0</v>
       </c>
       <c r="Z115" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA115" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC115" t="s">
         <v>1747</v>
@@ -15323,10 +15332,10 @@
         <v>0</v>
       </c>
       <c r="Z116" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA116" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB116" t="s">
         <v>1744</v>
@@ -15664,10 +15673,10 @@
         <v>0</v>
       </c>
       <c r="Z120" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA120" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB120" t="s">
         <v>1745</v>
@@ -15753,10 +15762,10 @@
         <v>0</v>
       </c>
       <c r="Z121" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA121" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB121" t="s">
         <v>1744</v>
@@ -16005,10 +16014,10 @@
         <v>0</v>
       </c>
       <c r="Z124" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA124" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB124" t="s">
         <v>1743</v>
@@ -16094,10 +16103,10 @@
         <v>0</v>
       </c>
       <c r="Z125" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA125" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB125" t="s">
         <v>1744</v>
@@ -16429,10 +16438,10 @@
         <v>0</v>
       </c>
       <c r="Z129" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA129" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB129" t="s">
         <v>1745</v>
@@ -16515,10 +16524,10 @@
         <v>0</v>
       </c>
       <c r="Z130" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA130" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB130" t="s">
         <v>1743</v>
@@ -16589,7 +16598,7 @@
         <v>0</v>
       </c>
       <c r="U131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W131" t="b">
         <v>0</v>
@@ -16684,10 +16693,10 @@
         <v>0</v>
       </c>
       <c r="Z132" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA132" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB132" t="s">
         <v>1745</v>
@@ -16859,10 +16868,10 @@
         <v>0</v>
       </c>
       <c r="Z134" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA134" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC134" t="s">
         <v>1747</v>
@@ -17108,10 +17117,10 @@
         <v>0</v>
       </c>
       <c r="Z137" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA137" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AC137" t="s">
         <v>1747</v>
@@ -17194,10 +17203,10 @@
         <v>0</v>
       </c>
       <c r="Z138" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA138" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB138" t="s">
         <v>1744</v>
@@ -17443,10 +17452,10 @@
         <v>0</v>
       </c>
       <c r="Z141" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA141" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC141" t="s">
         <v>1747</v>
@@ -17529,10 +17538,10 @@
         <v>0</v>
       </c>
       <c r="Z142" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA142" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB142" t="s">
         <v>1745</v>
@@ -17695,10 +17704,10 @@
         <v>0</v>
       </c>
       <c r="Z144" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA144" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AC144" t="s">
         <v>1747</v>
@@ -17870,10 +17879,10 @@
         <v>0</v>
       </c>
       <c r="Z146" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA146" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB146" t="s">
         <v>1745</v>
@@ -17944,7 +17953,7 @@
         <v>0</v>
       </c>
       <c r="U147" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W147" t="b">
         <v>0</v>
@@ -18036,10 +18045,10 @@
         <v>0</v>
       </c>
       <c r="Z148" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA148" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC148" t="s">
         <v>1747</v>
@@ -18297,10 +18306,10 @@
         <v>0</v>
       </c>
       <c r="Z151" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA151" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC151" t="s">
         <v>1747</v>
@@ -18460,10 +18469,10 @@
         <v>0</v>
       </c>
       <c r="Z153" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA153" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB153" t="s">
         <v>1744</v>
@@ -18623,10 +18632,10 @@
         <v>0</v>
       </c>
       <c r="Z155" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA155" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB155" t="s">
         <v>1745</v>
@@ -18792,10 +18801,10 @@
         <v>0</v>
       </c>
       <c r="Z157" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA157" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AC157" t="s">
         <v>1747</v>
@@ -18967,10 +18976,10 @@
         <v>0</v>
       </c>
       <c r="Z159" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA159" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB159" t="s">
         <v>1745</v>
@@ -19133,10 +19142,10 @@
         <v>0</v>
       </c>
       <c r="Z161" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA161" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB161" t="s">
         <v>1745</v>
@@ -19379,10 +19388,10 @@
         <v>0</v>
       </c>
       <c r="Z164" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA164" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB164" t="s">
         <v>1744</v>
@@ -19453,7 +19462,7 @@
         <v>1</v>
       </c>
       <c r="U165" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V165" t="b">
         <v>0</v>
@@ -19468,10 +19477,10 @@
         <v>0</v>
       </c>
       <c r="Z165" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA165" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB165" t="s">
         <v>1743</v>
@@ -19557,10 +19566,10 @@
         <v>0</v>
       </c>
       <c r="Z166" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA166" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB166" t="s">
         <v>1745</v>
@@ -19797,10 +19806,10 @@
         <v>0</v>
       </c>
       <c r="Z169" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA169" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB169" t="s">
         <v>1745</v>
@@ -19960,10 +19969,10 @@
         <v>0</v>
       </c>
       <c r="Z171" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA171" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC171" t="s">
         <v>1747</v>
@@ -20218,10 +20227,10 @@
         <v>0</v>
       </c>
       <c r="Z174" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA174" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB174" t="s">
         <v>1744</v>
@@ -20384,10 +20393,10 @@
         <v>0</v>
       </c>
       <c r="Z176" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA176" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AC176" t="s">
         <v>1747</v>
@@ -20559,10 +20568,10 @@
         <v>0</v>
       </c>
       <c r="Z178" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA178" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB178" t="s">
         <v>1744</v>
@@ -20722,10 +20731,10 @@
         <v>0</v>
       </c>
       <c r="Z180" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA180" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AC180" t="s">
         <v>1747</v>
@@ -20897,10 +20906,10 @@
         <v>0</v>
       </c>
       <c r="Z182" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA182" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB182" t="s">
         <v>1745</v>
@@ -21060,10 +21069,10 @@
         <v>0</v>
       </c>
       <c r="Z184" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA184" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC184" t="s">
         <v>1747</v>
@@ -21306,10 +21315,10 @@
         <v>0</v>
       </c>
       <c r="Z187" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA187" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC187" t="s">
         <v>1747</v>
@@ -21478,10 +21487,10 @@
         <v>0</v>
       </c>
       <c r="Z189" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA189" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB189" t="s">
         <v>1744</v>
@@ -21644,10 +21653,10 @@
         <v>0</v>
       </c>
       <c r="Z191" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA191" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC191" t="s">
         <v>1747</v>
@@ -21730,10 +21739,10 @@
         <v>0</v>
       </c>
       <c r="Z192" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA192" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB192" t="s">
         <v>1743</v>
@@ -21804,7 +21813,7 @@
         <v>1</v>
       </c>
       <c r="U193" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V193" t="b">
         <v>0</v>
@@ -21979,10 +21988,10 @@
         <v>0</v>
       </c>
       <c r="Z195" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA195" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AC195" t="s">
         <v>1747</v>
@@ -22154,10 +22163,10 @@
         <v>0</v>
       </c>
       <c r="Z197" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA197" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB197" t="s">
         <v>1745</v>
@@ -22320,10 +22329,10 @@
         <v>0</v>
       </c>
       <c r="Z199" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA199" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC199" t="s">
         <v>1747</v>
@@ -22566,10 +22575,10 @@
         <v>0</v>
       </c>
       <c r="Z202" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA202" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AC202" t="s">
         <v>1747</v>
@@ -22634,7 +22643,7 @@
         <v>1</v>
       </c>
       <c r="U203" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V203" t="b">
         <v>0</v>
@@ -22649,10 +22658,10 @@
         <v>0</v>
       </c>
       <c r="Z203" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA203" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB203" t="s">
         <v>1745</v>
@@ -22821,10 +22830,10 @@
         <v>0</v>
       </c>
       <c r="Z205" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA205" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC205" t="s">
         <v>1747</v>
@@ -23076,10 +23085,10 @@
         <v>0</v>
       </c>
       <c r="Z208" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA208" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB208" t="s">
         <v>1745</v>
@@ -23242,10 +23251,10 @@
         <v>0</v>
       </c>
       <c r="Z210" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA210" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC210" t="s">
         <v>1747</v>
@@ -23565,10 +23574,10 @@
         <v>0</v>
       </c>
       <c r="Z214" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA214" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AC214" t="s">
         <v>1747</v>
@@ -23648,10 +23657,10 @@
         <v>0</v>
       </c>
       <c r="Z215" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA215" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC215" t="s">
         <v>1747</v>
@@ -23903,10 +23912,10 @@
         <v>0</v>
       </c>
       <c r="Z218" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA218" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB218" t="s">
         <v>1744</v>
@@ -23992,10 +24001,10 @@
         <v>0</v>
       </c>
       <c r="Z219" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA219" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB219" t="s">
         <v>1745</v>
@@ -24164,10 +24173,10 @@
         <v>0</v>
       </c>
       <c r="Z221" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA221" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AC221" t="s">
         <v>1747</v>
@@ -24419,10 +24428,10 @@
         <v>0</v>
       </c>
       <c r="Z224" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA224" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB224" t="s">
         <v>1743</v>
@@ -24493,7 +24502,7 @@
         <v>0</v>
       </c>
       <c r="U225" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X225" t="b">
         <v>1</v>
@@ -24582,10 +24591,10 @@
         <v>0</v>
       </c>
       <c r="Z226" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA226" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB226" t="s">
         <v>1745</v>
@@ -24757,10 +24766,10 @@
         <v>0</v>
       </c>
       <c r="Z228" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA228" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC228" t="s">
         <v>1747</v>
@@ -24917,10 +24926,10 @@
         <v>0</v>
       </c>
       <c r="Z230" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA230" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC230" t="s">
         <v>1747</v>
@@ -25003,10 +25012,10 @@
         <v>0</v>
       </c>
       <c r="Z231" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA231" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB231" t="s">
         <v>1744</v>
@@ -25347,10 +25356,10 @@
         <v>0</v>
       </c>
       <c r="Z235" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA235" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AC235" t="s">
         <v>1747</v>
@@ -25507,10 +25516,10 @@
         <v>0</v>
       </c>
       <c r="Z237" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA237" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC237" t="s">
         <v>1747</v>
@@ -25590,10 +25599,10 @@
         <v>0</v>
       </c>
       <c r="Z238" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA238" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB238" t="s">
         <v>1744</v>
@@ -25839,10 +25848,10 @@
         <v>0</v>
       </c>
       <c r="Z241" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA241" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB241" t="s">
         <v>1744</v>
@@ -25928,10 +25937,10 @@
         <v>0</v>
       </c>
       <c r="Z242" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA242" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB242" t="s">
         <v>1743</v>
@@ -26174,10 +26183,10 @@
         <v>0</v>
       </c>
       <c r="Z245" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA245" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB245" t="s">
         <v>1744</v>
@@ -26423,10 +26432,10 @@
         <v>0</v>
       </c>
       <c r="Z248" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA248" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB248" t="s">
         <v>1743</v>
@@ -26509,10 +26518,10 @@
         <v>0</v>
       </c>
       <c r="Z249" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA249" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC249" t="s">
         <v>1747</v>
@@ -26761,10 +26770,10 @@
         <v>0</v>
       </c>
       <c r="Z252" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA252" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB252" t="s">
         <v>1743</v>
@@ -26850,10 +26859,10 @@
         <v>0</v>
       </c>
       <c r="Z253" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA253" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC253" t="s">
         <v>1747</v>
@@ -27096,10 +27105,10 @@
         <v>0</v>
       </c>
       <c r="Z256" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA256" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AC256" t="s">
         <v>1747</v>
@@ -27262,10 +27271,10 @@
         <v>0</v>
       </c>
       <c r="Z258" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA258" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB258" t="s">
         <v>1745</v>
@@ -27517,10 +27526,10 @@
         <v>0</v>
       </c>
       <c r="Z261" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA261" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC261" t="s">
         <v>1747</v>
@@ -27677,10 +27686,10 @@
         <v>0</v>
       </c>
       <c r="Z263" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA263" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB263" t="s">
         <v>1745</v>
@@ -27846,10 +27855,10 @@
         <v>0</v>
       </c>
       <c r="Z265" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA265" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC265" t="s">
         <v>1747</v>
@@ -28012,10 +28021,10 @@
         <v>0</v>
       </c>
       <c r="Z267" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA267" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB267" t="s">
         <v>1745</v>
@@ -28264,10 +28273,10 @@
         <v>0</v>
       </c>
       <c r="Z270" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA270" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC270" t="s">
         <v>1747</v>
@@ -28350,10 +28359,10 @@
         <v>0</v>
       </c>
       <c r="Z271" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA271" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB271" t="s">
         <v>1745</v>
@@ -28602,10 +28611,10 @@
         <v>0</v>
       </c>
       <c r="Z274" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA274" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB274" t="s">
         <v>1745</v>
@@ -28691,10 +28700,10 @@
         <v>0</v>
       </c>
       <c r="Z275" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA275" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB275" t="s">
         <v>1744</v>
@@ -29029,10 +29038,10 @@
         <v>0</v>
       </c>
       <c r="Z279" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA279" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC279" t="s">
         <v>1747</v>
@@ -29115,10 +29124,10 @@
         <v>0</v>
       </c>
       <c r="Z280" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA280" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB280" t="s">
         <v>1744</v>
@@ -29278,10 +29287,10 @@
         <v>0</v>
       </c>
       <c r="Z282" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA282" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB282" t="s">
         <v>1745</v>
@@ -29533,10 +29542,10 @@
         <v>0</v>
       </c>
       <c r="Z285" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA285" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB285" t="s">
         <v>1745</v>
@@ -29622,10 +29631,10 @@
         <v>0</v>
       </c>
       <c r="Z286" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA286" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB286" t="s">
         <v>1743</v>
@@ -29859,7 +29868,7 @@
         <v>1</v>
       </c>
       <c r="U289" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V289" t="b">
         <v>0</v>
@@ -29871,10 +29880,10 @@
         <v>0</v>
       </c>
       <c r="Z289" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA289" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC289" t="s">
         <v>1747</v>
@@ -30031,10 +30040,10 @@
         <v>0</v>
       </c>
       <c r="Z291" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA291" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB291" t="s">
         <v>1744</v>
@@ -30289,10 +30298,10 @@
         <v>0</v>
       </c>
       <c r="Z294" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA294" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB294" t="s">
         <v>1743</v>
@@ -30452,10 +30461,10 @@
         <v>0</v>
       </c>
       <c r="Z296" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA296" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB296" t="s">
         <v>1745</v>
@@ -30710,10 +30719,10 @@
         <v>0</v>
       </c>
       <c r="Z299" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA299" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC299" t="s">
         <v>1747</v>
@@ -30867,7 +30876,7 @@
         <v>1</v>
       </c>
       <c r="U301" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V301" t="b">
         <v>0</v>
@@ -30879,10 +30888,10 @@
         <v>0</v>
       </c>
       <c r="Z301" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA301" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC301" t="s">
         <v>1747</v>
@@ -31039,10 +31048,10 @@
         <v>0</v>
       </c>
       <c r="Z303" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA303" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AC303" t="s">
         <v>1747</v>
@@ -31294,10 +31303,10 @@
         <v>0</v>
       </c>
       <c r="Z306" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA306" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB306" t="s">
         <v>1744</v>
@@ -31383,10 +31392,10 @@
         <v>0</v>
       </c>
       <c r="Z307" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA307" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AC307" t="s">
         <v>1747</v>
@@ -31638,10 +31647,10 @@
         <v>0</v>
       </c>
       <c r="Z310" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA310" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB310" t="s">
         <v>1745</v>
@@ -31721,10 +31730,10 @@
         <v>0</v>
       </c>
       <c r="Z311" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA311" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC311" t="s">
         <v>1747</v>
@@ -31961,10 +31970,10 @@
         <v>0</v>
       </c>
       <c r="Z314" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA314" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AC314" t="s">
         <v>1747</v>
@@ -32136,10 +32145,10 @@
         <v>0</v>
       </c>
       <c r="Z316" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA316" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB316" t="s">
         <v>1745</v>
@@ -32302,10 +32311,10 @@
         <v>0</v>
       </c>
       <c r="Z318" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA318" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC318" t="s">
         <v>1747</v>
@@ -32548,10 +32557,10 @@
         <v>0</v>
       </c>
       <c r="Z321" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA321" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB321" t="s">
         <v>1745</v>
@@ -32720,10 +32729,10 @@
         <v>0</v>
       </c>
       <c r="Z323" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA323" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC323" t="s">
         <v>1747</v>
@@ -32883,10 +32892,10 @@
         <v>0</v>
       </c>
       <c r="Z325" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA325" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC325" t="s">
         <v>1747</v>
@@ -33046,10 +33055,10 @@
         <v>0</v>
       </c>
       <c r="Z327" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA327" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB327" t="s">
         <v>1744</v>
@@ -33224,10 +33233,10 @@
         <v>0</v>
       </c>
       <c r="Z329" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA329" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB329" t="s">
         <v>1743</v>
@@ -33559,10 +33568,10 @@
         <v>0</v>
       </c>
       <c r="Z333" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA333" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB333" t="s">
         <v>1744</v>
@@ -33704,7 +33713,7 @@
         <v>1</v>
       </c>
       <c r="U335" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V335" t="b">
         <v>0</v>
@@ -33716,10 +33725,10 @@
         <v>0</v>
       </c>
       <c r="Z335" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA335" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AC335" t="s">
         <v>1747</v>
@@ -33802,10 +33811,10 @@
         <v>0</v>
       </c>
       <c r="Z336" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA336" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB336" t="s">
         <v>1745</v>
@@ -34054,10 +34063,10 @@
         <v>0</v>
       </c>
       <c r="Z339" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA339" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB339" t="s">
         <v>1745</v>
@@ -34128,7 +34137,7 @@
         <v>1</v>
       </c>
       <c r="U340" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V340" t="b">
         <v>0</v>
@@ -34143,16 +34152,16 @@
         <v>0</v>
       </c>
       <c r="Z340" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA340" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB340" t="s">
         <v>1744</v>
       </c>
       <c r="AC340" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="341" spans="1:29">
@@ -34291,7 +34300,7 @@
         <v>1</v>
       </c>
       <c r="U342" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V342" t="b">
         <v>0</v>
@@ -34395,10 +34404,10 @@
         <v>0</v>
       </c>
       <c r="Z343" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA343" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB343" t="s">
         <v>1743</v>
@@ -34481,10 +34490,10 @@
         <v>0</v>
       </c>
       <c r="Z344" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA344" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC344" t="s">
         <v>1747</v>
@@ -34623,7 +34632,7 @@
         <v>1</v>
       </c>
       <c r="U346" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V346" t="b">
         <v>0</v>
@@ -34647,7 +34656,7 @@
         <v>1745</v>
       </c>
       <c r="AC346" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="347" spans="1:29">
@@ -34727,10 +34736,10 @@
         <v>0</v>
       </c>
       <c r="Z347" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA347" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB347" t="s">
         <v>1744</v>
@@ -34976,10 +34985,10 @@
         <v>0</v>
       </c>
       <c r="Z350" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA350" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB350" t="s">
         <v>1743</v>
@@ -35148,10 +35157,10 @@
         <v>0</v>
       </c>
       <c r="Z352" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA352" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC352" t="s">
         <v>1747</v>
@@ -35302,10 +35311,10 @@
         <v>0</v>
       </c>
       <c r="Z354" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA354" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AC354" t="s">
         <v>1747</v>
@@ -35373,7 +35382,7 @@
         <v>1</v>
       </c>
       <c r="U355" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V355" t="b">
         <v>0</v>
@@ -35542,10 +35551,10 @@
         <v>0</v>
       </c>
       <c r="Z357" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA357" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB357" t="s">
         <v>1744</v>
@@ -35631,10 +35640,10 @@
         <v>0</v>
       </c>
       <c r="Z358" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA358" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB358" t="s">
         <v>1745</v>
@@ -35865,7 +35874,7 @@
         <v>1</v>
       </c>
       <c r="U361" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V361" t="b">
         <v>0</v>
@@ -35880,16 +35889,16 @@
         <v>0</v>
       </c>
       <c r="Z361" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA361" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB361" t="s">
         <v>1745</v>
       </c>
       <c r="AC361" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="362" spans="1:29">
@@ -36028,7 +36037,7 @@
         <v>1</v>
       </c>
       <c r="U363" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V363" t="b">
         <v>0</v>
@@ -36040,10 +36049,10 @@
         <v>0</v>
       </c>
       <c r="Z363" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA363" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC363" t="s">
         <v>1747</v>
@@ -36212,10 +36221,10 @@
         <v>0</v>
       </c>
       <c r="Z365" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA365" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB365" t="s">
         <v>1743</v>
@@ -36375,10 +36384,10 @@
         <v>0</v>
       </c>
       <c r="Z367" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA367" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB367" t="s">
         <v>1744</v>
@@ -36461,10 +36470,10 @@
         <v>0</v>
       </c>
       <c r="Z368" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA368" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB368" t="s">
         <v>1744</v>
@@ -36707,10 +36716,10 @@
         <v>0</v>
       </c>
       <c r="Z371" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA371" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB371" t="s">
         <v>1743</v>
@@ -37039,10 +37048,10 @@
         <v>0</v>
       </c>
       <c r="Z375" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA375" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC375" t="s">
         <v>1747</v>
@@ -37205,10 +37214,10 @@
         <v>0</v>
       </c>
       <c r="Z377" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA377" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB377" t="s">
         <v>1743</v>
@@ -37377,10 +37386,10 @@
         <v>0</v>
       </c>
       <c r="Z379" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA379" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB379" t="s">
         <v>1744</v>
@@ -37540,10 +37549,10 @@
         <v>0</v>
       </c>
       <c r="Z381" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA381" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB381" t="s">
         <v>1745</v>
@@ -37786,10 +37795,10 @@
         <v>0</v>
       </c>
       <c r="Z384" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA384" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB384" t="s">
         <v>1744</v>
@@ -37955,10 +37964,10 @@
         <v>0</v>
       </c>
       <c r="Z386" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA386" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB386" t="s">
         <v>1745</v>
@@ -38118,10 +38127,10 @@
         <v>0</v>
       </c>
       <c r="Z388" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA388" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC388" t="s">
         <v>1747</v>
@@ -38367,10 +38376,10 @@
         <v>0</v>
       </c>
       <c r="Z391" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA391" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB391" t="s">
         <v>1744</v>
@@ -38456,10 +38465,10 @@
         <v>0</v>
       </c>
       <c r="Z392" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA392" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC392" t="s">
         <v>1747</v>
@@ -38616,7 +38625,7 @@
         <v>0</v>
       </c>
       <c r="U394" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X394" t="b">
         <v>1</v>
@@ -38702,10 +38711,10 @@
         <v>0</v>
       </c>
       <c r="Z395" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA395" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC395" t="s">
         <v>1747</v>
@@ -39040,10 +39049,10 @@
         <v>0</v>
       </c>
       <c r="Z399" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA399" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB399" t="s">
         <v>1745</v>
@@ -39123,10 +39132,10 @@
         <v>0</v>
       </c>
       <c r="Z400" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA400" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AC400" t="s">
         <v>1747</v>
@@ -39286,10 +39295,10 @@
         <v>0</v>
       </c>
       <c r="Z402" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA402" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB402" t="s">
         <v>1745</v>
@@ -39372,10 +39381,10 @@
         <v>0</v>
       </c>
       <c r="Z403" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA403" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC403" t="s">
         <v>1747</v>
@@ -39624,10 +39633,10 @@
         <v>0</v>
       </c>
       <c r="Z406" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA406" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB406" t="s">
         <v>1745</v>
@@ -39713,10 +39722,10 @@
         <v>0</v>
       </c>
       <c r="Z407" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA407" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB407" t="s">
         <v>1743</v>
@@ -39959,10 +39968,10 @@
         <v>0</v>
       </c>
       <c r="Z410" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA410" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB410" t="s">
         <v>1744</v>
@@ -40122,10 +40131,10 @@
         <v>0</v>
       </c>
       <c r="Z412" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA412" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB412" t="s">
         <v>1744</v>
@@ -40451,10 +40460,10 @@
         <v>0</v>
       </c>
       <c r="Z416" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA416" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB416" t="s">
         <v>1745</v>
@@ -40540,10 +40549,10 @@
         <v>0</v>
       </c>
       <c r="Z417" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA417" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB417" t="s">
         <v>1743</v>
@@ -40795,10 +40804,10 @@
         <v>0</v>
       </c>
       <c r="Z420" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA420" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB420" t="s">
         <v>1744</v>
@@ -41032,10 +41041,10 @@
         <v>0</v>
       </c>
       <c r="Z423" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA423" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB423" t="s">
         <v>1745</v>
@@ -41121,10 +41130,10 @@
         <v>0</v>
       </c>
       <c r="Z424" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA424" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB424" t="s">
         <v>1744</v>
@@ -41373,10 +41382,10 @@
         <v>0</v>
       </c>
       <c r="Z427" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA427" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC427" t="s">
         <v>1747</v>
@@ -41459,10 +41468,10 @@
         <v>0</v>
       </c>
       <c r="Z428" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA428" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB428" t="s">
         <v>1744</v>
@@ -41616,10 +41625,10 @@
         <v>0</v>
       </c>
       <c r="Z430" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA430" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC430" t="s">
         <v>1747</v>
@@ -41782,10 +41791,10 @@
         <v>0</v>
       </c>
       <c r="Z432" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA432" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC432" t="s">
         <v>1747</v>
@@ -41951,10 +41960,10 @@
         <v>0</v>
       </c>
       <c r="Z434" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA434" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB434" t="s">
         <v>1743</v>
@@ -42277,10 +42286,10 @@
         <v>0</v>
       </c>
       <c r="Z438" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA438" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB438" t="s">
         <v>1744</v>
@@ -42443,10 +42452,10 @@
         <v>0</v>
       </c>
       <c r="Z440" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA440" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AC440" t="s">
         <v>1747</v>
@@ -42615,10 +42624,10 @@
         <v>0</v>
       </c>
       <c r="Z442" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA442" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC442" t="s">
         <v>1747</v>
@@ -42772,10 +42781,10 @@
         <v>0</v>
       </c>
       <c r="Z444" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA444" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB444" t="s">
         <v>1745</v>
@@ -43027,10 +43036,10 @@
         <v>0</v>
       </c>
       <c r="Z447" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA447" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB447" t="s">
         <v>1745</v>
@@ -43098,7 +43107,7 @@
         <v>1</v>
       </c>
       <c r="U448" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V448" t="b">
         <v>0</v>
@@ -43110,10 +43119,10 @@
         <v>0</v>
       </c>
       <c r="Z448" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA448" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC448" t="s">
         <v>1747</v>
@@ -43347,10 +43356,10 @@
         <v>0</v>
       </c>
       <c r="Z451" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA451" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB451" t="s">
         <v>1744</v>
@@ -43602,10 +43611,10 @@
         <v>0</v>
       </c>
       <c r="Z454" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA454" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC454" t="s">
         <v>1747</v>
@@ -43682,10 +43691,10 @@
         <v>0</v>
       </c>
       <c r="Z455" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA455" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB455" t="s">
         <v>1745</v>
@@ -44020,10 +44029,10 @@
         <v>0</v>
       </c>
       <c r="Z459" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA459" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC459" t="s">
         <v>1747</v>
@@ -44186,10 +44195,10 @@
         <v>0</v>
       </c>
       <c r="Z461" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA461" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB461" t="s">
         <v>1743</v>
@@ -44352,10 +44361,10 @@
         <v>0</v>
       </c>
       <c r="Z463" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA463" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AC463" t="s">
         <v>1747</v>
@@ -44512,10 +44521,10 @@
         <v>0</v>
       </c>
       <c r="Z465" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA465" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB465" t="s">
         <v>1744</v>
@@ -44755,10 +44764,10 @@
         <v>0</v>
       </c>
       <c r="Z468" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA468" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB468" t="s">
         <v>1743</v>
@@ -44841,10 +44850,10 @@
         <v>0</v>
       </c>
       <c r="Z469" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA469" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC469" t="s">
         <v>1747</v>
@@ -45007,10 +45016,10 @@
         <v>0</v>
       </c>
       <c r="Z471" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA471" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB471" t="s">
         <v>1744</v>
@@ -45256,10 +45265,10 @@
         <v>0</v>
       </c>
       <c r="Z474" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA474" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB474" t="s">
         <v>1745</v>
@@ -45585,10 +45594,10 @@
         <v>0</v>
       </c>
       <c r="Z478" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA478" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB478" t="s">
         <v>1745</v>
@@ -45674,10 +45683,10 @@
         <v>0</v>
       </c>
       <c r="Z479" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA479" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB479" t="s">
         <v>1743</v>
@@ -45926,10 +45935,10 @@
         <v>0</v>
       </c>
       <c r="Z482" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA482" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB482" t="s">
         <v>1744</v>
@@ -46009,10 +46018,10 @@
         <v>0</v>
       </c>
       <c r="Z483" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA483" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB483" t="s">
         <v>1744</v>
@@ -46172,10 +46181,10 @@
         <v>0</v>
       </c>
       <c r="Z485" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA485" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB485" t="s">
         <v>1745</v>
@@ -46243,7 +46252,7 @@
         <v>0</v>
       </c>
       <c r="U486" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W486" t="b">
         <v>1</v>
@@ -46421,10 +46430,10 @@
         <v>0</v>
       </c>
       <c r="Z488" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA488" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB488" t="s">
         <v>1743</v>
@@ -46667,10 +46676,10 @@
         <v>0</v>
       </c>
       <c r="Z491" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA491" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB491" t="s">
         <v>1745</v>
@@ -46756,10 +46765,10 @@
         <v>0</v>
       </c>
       <c r="Z492" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA492" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB492" t="s">
         <v>1744</v>
@@ -46996,10 +47005,10 @@
         <v>0</v>
       </c>
       <c r="Z495" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AA495" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="AB495" t="s">
         <v>1743</v>
@@ -47079,10 +47088,10 @@
         <v>0</v>
       </c>
       <c r="Z496" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA496" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AC496" t="s">
         <v>1747</v>
@@ -47396,7 +47405,7 @@
         <v>1</v>
       </c>
       <c r="U500" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V500" t="b">
         <v>0</v>
@@ -47411,16 +47420,16 @@
         <v>0</v>
       </c>
       <c r="Z500" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AA500" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AB500" t="s">
         <v>1745</v>
       </c>
       <c r="AC500" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
     </row>
   </sheetData>

--- a/data/cleaned_data.xlsx
+++ b/data/cleaned_data.xlsx
@@ -5874,7 +5874,7 @@
         <v>35</v>
       </c>
       <c r="E4">
-        <v>7501</v>
+        <v>7500</v>
       </c>
       <c r="F4">
         <v>0</v>
